--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M405"/>
+  <dimension ref="A1:M406"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="39" min="1" max="1"/>
@@ -2182,17 +2182,17 @@
           <t>Postulate</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>Rests On</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>Sign-Critical</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>Last Verified</t>
         </is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="J6" s="41" t="n"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="J9" s="41" t="n"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I13" s="41" t="n"/>
       <c r="J13" s="41" t="n"/>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="J18" s="41" t="n"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="J19" s="41" t="n"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="I20" s="41" t="n"/>
       <c r="J20" s="41" t="n"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="0" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="J22" s="41" t="n"/>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="J23" s="41" t="n"/>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="J28" s="41" t="n"/>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="J31" s="41" t="n"/>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3787,12 +3787,12 @@
         </is>
       </c>
       <c r="J41" s="41" t="n"/>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_BH_Thermal2Pi_EntropyCoefficient.md declares no censused postulate (mechanical check only, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3837,12 +3837,12 @@
         </is>
       </c>
       <c r="J42" s="41" t="n"/>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Constants_Ledger_and_G_Dimension.md declares P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3891,12 +3891,12 @@
         </is>
       </c>
       <c r="J43" s="41" t="n"/>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_ED_Baryogenesis.md declares P-BinaryAdmission. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I44" s="41" t="n"/>
       <c r="J44" s="41" t="n"/>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_ED_Cos_06_InflationarySpectrum.md declares P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -3990,12 +3990,12 @@
         </is>
       </c>
       <c r="J45" s="41" t="n"/>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_029_a0.md declares P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -4048,12 +4048,12 @@
         </is>
       </c>
       <c r="J46" s="41" t="n"/>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_ED_DarkSector.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="0" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -4106,12 +4106,12 @@
         </is>
       </c>
       <c r="J47" s="41" t="n"/>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_ED_RelicLagrangian_v1.md declares no censused postulate (mechanical check only, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -4160,12 +4160,12 @@
         </is>
       </c>
       <c r="J48" s="41" t="n"/>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_ED_RelicLagrangian_v1.md declares no censused postulate (mechanical check only, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -4210,12 +4210,12 @@
         </is>
       </c>
       <c r="J49" s="41" t="n"/>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_ED_RelicLagrangian_v1.md declares no censused postulate (mechanical check only, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D50" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E50" s="41" t="n"/>
@@ -4260,9 +4260,9 @@
       </c>
       <c r="I50" s="41" t="n"/>
       <c r="J50" s="41" t="n"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>CANDIDATE - Paper_064_SchmidtDecomposition.md declares P-Bipartite-Mapping, P-V5-Schmidt-Generic. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t>P-V5-Schmidt-Generic AND P-Bipartite-Mapping. VERIFIED 2026-09-06 (#124), read against the paper's own audit table. Paper_064 audit rows 2 and 8 are both labelled P; the D row (rank&gt;1 =&gt; non-factorizable) sits on top of them and the paper's own conclusion reads 'under standard SVD inheritance + P-V5-Schmidt-Generic'. NOTE: the sheet named only P-V5-Schmidt-Generic; P-Bipartite-Mapping supplies the arena and was missing. [re-tiered Derived -&gt; Grounded]</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4279,12 @@
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Monogamy (CKW-form inequality)</t>
+          <t>Monogamy: total pairwise entanglement capped by the chain's V5 budget (Sum_i E_{A,Bi} &lt;= W_max)</t>
         </is>
       </c>
       <c r="D51" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E51" s="41" t="n"/>
@@ -4295,19 +4295,19 @@
       </c>
       <c r="G51" s="41" t="inlineStr">
         <is>
-          <t>conditional on P-V5-Budget + P-Measure-Saturation; coefficient inherited</t>
+          <t>conditional on P-V5-Budget + P-Measure-Saturation; W_max inherited</t>
         </is>
       </c>
       <c r="H51" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current - narrowed 2026-09-04; sheet row updated 2026-09-06</t>
         </is>
       </c>
       <c r="I51" s="41" t="n"/>
       <c r="J51" s="41" t="n"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>CANDIDATE - Paper_065_Monogamy.md declares P-Measure-Saturation, P-V5-Budget. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t>P-V5-Budget, P-Measure-Saturation; W_max inherited. VERIFIED 2026-09-06 (#124), read against the paper's own audit table. STALE ROW: the claim previously read 'Monogamy (CKW-form inequality)'. Paper_065 and the entanglement arc ledger BOTH narrowed this on 2026-09-04 and split it in two; the sheet kept the pre-split wording. This row is now the half that IS derived. [re-tiered Derived -&gt; Grounded, claim narrowed]</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="D52" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E52" s="41" t="n"/>
@@ -4354,12 +4354,12 @@
         </is>
       </c>
       <c r="J52" s="41" t="n"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>CANDIDATE - Paper_066_NoSignaling.md declares P-Bipartite-Mapping, P-Substrate-Causality. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
+        <is>
+          <t>P-Bipartite-Mapping (audit rows 1 and 3) AND P-Substrate-Causality (audit row 4). VERIFIED 2026-09-06 (#124), read against the paper's own audit table. Locks L1/L2 are D-via-I, L3 is I, and the composite verdict '3 locks =&gt; over-determination' is the paper's own A-&gt;position (audit row 10). CLAIM CONFLATES TWO THINGS: no-signaling (Grounded) and the over-determination verdict (Asserted). Worth splitting. [re-tiered Derived -&gt; Grounded]</t>
+        </is>
+      </c>
+      <c r="M52" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D53" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E53" s="41" t="n"/>
@@ -4404,9 +4404,9 @@
       </c>
       <c r="I53" s="41" t="n"/>
       <c r="J53" s="41" t="n"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>CANDIDATE - Paper_068_VonNeumannEntropy.md declares P-Additivity, P-Continuity, P-Maximality. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+      <c r="K53" s="0" t="inlineStr">
+        <is>
+          <t>P-Continuity, P-Additivity, P-Maximality (audit rows 3-5, all P); normalization inherited. VERIFIED 2026-09-06 (#124), read against the paper's own audit table. The sheet's own Derived column already read 'D-via-I', contradicting the Derived tier. P-Maximality's derivation (O-vN-2) is not merely open but STRUCTURALLY BLOCKED - ED has no substrate-level temperature. [re-tiered Derived -&gt; Grounded]</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="I54" s="41" t="n"/>
       <c r="J54" s="41" t="n"/>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_089_V1Kernel.md declares P-NoBackwardChain, P-SubstrateLocality. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -4498,12 +4498,12 @@
         </is>
       </c>
       <c r="J55" s="41" t="n"/>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_089_V1Kernel.md, Paper_093_KernelArrow_of_Time.md declares P-NoBackwardChain, P-SubstrateLocality, P-T18-Arrow-Inheritance, P-T18-Kernel-Retardation. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M55" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="I56" s="41" t="n"/>
       <c r="J56" s="41" t="n"/>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_089_V1Kernel.md, Paper_093_KernelArrow_of_Time.md declares P-NoBackwardChain, P-SubstrateLocality, P-T18-Arrow-Inheritance, P-T18-Kernel-Retardation. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="I57" s="41" t="n"/>
       <c r="J57" s="41" t="n"/>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_090_V5Kernel.md, Paper_094_ForwardCausality.md declares P-Causality-Propagation, P-Primitive-Forward-Causality. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I58" s="41" t="n"/>
       <c r="J58" s="41" t="n"/>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_025_HolographicBound.md declares P-Codim-1, P-Sat. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I59" s="41" t="n"/>
       <c r="J59" s="41" t="n"/>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_026_CumulativeStrain.md declares P-Codim-1, P-Potential-Reading, P-Sat. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="I60" s="41" t="n"/>
       <c r="J60" s="41" t="n"/>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_032_5_FreeChainGeodesics.md declares P-FreeChain. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="I61" s="41" t="n"/>
       <c r="J61" s="41" t="n"/>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_034_DeepMOND.md, Paper_036_MOND_FieldEquation.md declares P-Codim-1, P-MOND-Field-Form, P-MOND-Interpolation, P-No-New-Primitive. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M61" s="0" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="I62" s="41" t="n"/>
       <c r="J62" s="41" t="n"/>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_037_a0_Invariance.md declares P-H0-Cosmological-Invariant, P-Profile-Rescaling, P-RB-1, P-Substrate-c-Constancy. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -4872,12 +4872,12 @@
         </is>
       </c>
       <c r="J63" s="41" t="n"/>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="0" t="inlineStr">
         <is>
           <t>P-Commitment-Linear. VERIFIED 2026-09-06 (#122): GR-I preamble 6 -- 'the lapse derivation rests on a stated postulate (P-Commitment-Linear, section 2) ... the load-bearing structural commitment selecting the Einstein branch'.  [re-tiered Derived -&gt; Grounded, 2026-09-06, gravity ledger #122]</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M63" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="I64" s="41" t="n"/>
       <c r="J64" s="41" t="n"/>
-      <c r="K64" t="inlineStr">
+      <c r="K64" s="0" t="inlineStr">
         <is>
           <t>P-Commitment-Linear. VERIFIED 2026-09-06 (#122): same lapse chain as row 63.  [re-tiered Derived -&gt; Grounded, 2026-09-06, gravity ledger #122]</t>
         </is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I65" s="41" t="n"/>
       <c r="J65" s="41" t="n"/>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="0" t="inlineStr">
         <is>
           <t>Lovelock uniqueness (conditional) + inherited kappa, Lambda. VERIFIED 2026-09-06 (#122): GR-II preamble 2 makes the form conditional; preamble 7 -- 'kappa = 8 pi G and Lambda are inherited, not derived'. Form derived, values inherited.  [re-tiered Derived -&gt; D-via-I / Form-forced, 2026-09-06, gravity ledger #122]</t>
         </is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="I66" s="41" t="n"/>
       <c r="J66" s="41" t="n"/>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_GR-II_KhronometricClass.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="I67" s="41" t="n"/>
       <c r="J67" s="41" t="n"/>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_GR-II_KhronometricClass.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I68" s="41" t="n"/>
       <c r="J68" s="41" t="n"/>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_GR-II_KhronometricClass.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="I69" s="41" t="n"/>
       <c r="J69" s="41" t="n"/>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="0" t="inlineStr">
         <is>
           <t>P-Commitment-Linear. VERIFIED 2026-09-06 (#122): the claim text itself names the postulate. Self-contradicting as filed.  [re-tiered Derived -&gt; Postulated, 2026-09-06, gravity ledger #122]</t>
         </is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="I70" s="41" t="n"/>
       <c r="J70" s="41" t="n"/>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_GR-III_DynamicalRule.md declares P-Commitment-Linear. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5241,12 +5241,12 @@
         </is>
       </c>
       <c r="J71" s="41" t="n"/>
-      <c r="K71" t="inlineStr">
+      <c r="K71" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_GR-IV_ArrowsAlibi.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M71" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="I72" s="41" t="n"/>
       <c r="J72" s="41" t="n"/>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_GR-IV_ArrowsAlibi.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5340,12 +5340,12 @@
         </is>
       </c>
       <c r="J73" s="41" t="n"/>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_MetricFromTheGraph_ForcedTo3D.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M73" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I74" s="41" t="n"/>
       <c r="J74" s="41" t="n"/>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_054_UR1.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="I75" s="41" t="n"/>
       <c r="J75" s="41" t="n"/>
-      <c r="K75" t="inlineStr">
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_054_UR1.md, Paper_056_ClassA_Wall.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -5484,12 +5484,12 @@
         </is>
       </c>
       <c r="J76" s="41" t="n"/>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_058b_PlateauDomain_AlphaTopological.md declares P-Corr-Budget, P-QD-LiveWeight, P-Redundancy-Mapping. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M76" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="I77" s="41" t="n"/>
       <c r="J77" s="41" t="n"/>
-      <c r="K77" t="inlineStr">
+      <c r="K77" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_058b_PlateauDomain_AlphaTopological.md declares P-Corr-Budget, P-QD-LiveWeight, P-Redundancy-Mapping. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
         </is>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="I78" s="41" t="n"/>
       <c r="J78" s="41" t="n"/>
-      <c r="K78" t="inlineStr">
+      <c r="K78" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_016_MinimalCoupling.md declares P-Bundle-Definition, P-Connection-Naming, P-Fiber-Naming, P-NonAbelian-Analogy. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="I79" s="41" t="n"/>
       <c r="J79" s="41" t="n"/>
-      <c r="K79" t="inlineStr">
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_017_FreeScalarQFT.md declares P-Lorentz-Covariant-Continuum, P-Scalar-Match. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I80" s="41" t="n"/>
       <c r="J80" s="41" t="n"/>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t>P-YM-Action-Coarse-Graining. VERIFIED 2026-09-06 (#122): Paper_019 section 3.4 -- 'standard variational derivation from the P-postulated action ... the action itself is constructed via P-YM-Action-Coarse-Graining'.  [re-tiered Derived -&gt; Grounded, 2026-09-06, gravity ledger #122]</t>
         </is>
@@ -5710,12 +5710,12 @@
         </is>
       </c>
       <c r="J81" s="41" t="n"/>
-      <c r="K81" t="inlineStr">
+      <c r="K81" s="0" t="inlineStr">
         <is>
           <t>P-Gap-Coercivity, P-Profile-Rescaling, P-Quartic-Sign. VERIFIED 2026-09-06 (#122): Paper_023 -- 'Mass-gap mechanism with P-Gap-Coercivity, P-Profile-Rescaling, P-Quartic-Sign (Paper_021)'.  [re-tiered Derived -&gt; Grounded, 2026-09-06, gravity ledger #122]</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M81" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I82" s="41" t="n"/>
       <c r="J82" s="41" t="n"/>
-      <c r="K82" t="inlineStr">
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_022_YM5_GaugeQuotient.md declares P-Gauge-Orbit-Non-Empty, P-Quotient-Hilbert. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="I83" s="41" t="n"/>
       <c r="J83" s="41" t="n"/>
-      <c r="K83" t="inlineStr">
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_024_LindbladLimit.md declares P-Factorized-IC, P-Markovian, P-Weak-Coupling. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -5854,12 +5854,12 @@
         </is>
       </c>
       <c r="J84" s="41" t="n"/>
-      <c r="K84" t="inlineStr">
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_MS-II_MatterSectorFromTheArrow.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="M84" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -5908,12 +5908,12 @@
         </is>
       </c>
       <c r="J85" s="41" t="n"/>
-      <c r="K85" t="inlineStr">
+      <c r="K85" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_001_PreIndividuation.md declares P-LinRate, P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M85" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="I86" s="41" t="n"/>
       <c r="J86" s="41" t="n"/>
-      <c r="K86" t="inlineStr">
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_009_BerryPhase.md declares P-Adiabatic-Coarse-Graining, P-Loop-Closure. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I87" s="41" t="n"/>
       <c r="J87" s="41" t="n"/>
-      <c r="K87" t="inlineStr">
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_010_AharonovBohm.md declares P-Excluded-Region, P-Flat-Outside. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="I88" s="41" t="n"/>
       <c r="J88" s="41" t="n"/>
-      <c r="K88" t="inlineStr">
+      <c r="K88" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_011_BlochTheorem.md declares P-Discrete-Translation, P-Symmetric-Hamiltonian. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
         </is>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="I89" s="41" t="n"/>
       <c r="J89" s="41" t="n"/>
-      <c r="K89" t="inlineStr">
+      <c r="K89" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_012_7_AdjacencyBandwidth_Galilean.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -6142,12 +6142,12 @@
         </is>
       </c>
       <c r="J90" s="41" t="n"/>
-      <c r="K90" t="inlineStr">
+      <c r="K90" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_103_Cl31_FrameUniqueness.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M90" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6200,12 +6200,12 @@
         </is>
       </c>
       <c r="J91" s="41" t="n"/>
-      <c r="K91" t="inlineStr">
+      <c r="K91" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_104_AnyonProhibition.md declares no censused postulate (mechanical check only, 2026-09-06; resolved EXACT)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M91" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6254,12 +6254,12 @@
         </is>
       </c>
       <c r="J92" s="41" t="n"/>
-      <c r="K92" t="inlineStr">
+      <c r="K92" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_CommonCauseNotChannel_A1.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M92" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="I93" s="41" t="n"/>
       <c r="J93" s="41" t="n"/>
-      <c r="K93" t="inlineStr">
+      <c r="K93" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_ChargeAsTopology_B4.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
         </is>
@@ -6353,17 +6353,17 @@
         </is>
       </c>
       <c r="J94" s="41" t="n"/>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="0" t="inlineStr">
         <is>
           <t>none found - Paper_CleanSubstrateVector_ParitySpontaneous.md declares no censused postulate (mechanical check only, 2026-09-06; resolved FUZZY)</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="L94" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="M94" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="I95" s="41" t="n"/>
       <c r="J95" s="41" t="n"/>
-      <c r="K95" t="inlineStr">
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - Paper_QuantumDarwinism_RecordBandwidth.md declares P-QD-LiveWeight, P-V5-Budget. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
         </is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="J100" s="41" t="n"/>
-      <c r="M100" t="inlineStr">
+      <c r="M100" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="J101" s="41" t="n"/>
-      <c r="M101" t="inlineStr">
+      <c r="M101" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="J103" s="41" t="n"/>
-      <c r="M103" t="inlineStr">
+      <c r="M103" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="J104" s="41" t="n"/>
-      <c r="M104" t="inlineStr">
+      <c r="M104" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="J105" s="41" t="n"/>
-      <c r="M105" t="inlineStr">
+      <c r="M105" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="J106" s="41" t="n"/>
-      <c r="M106" t="inlineStr">
+      <c r="M106" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="J107" s="41" t="n"/>
-      <c r="M107" t="inlineStr">
+      <c r="M107" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="J109" s="41" t="n"/>
-      <c r="M109" t="inlineStr">
+      <c r="M109" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="J112" s="41" t="n"/>
-      <c r="M112" t="inlineStr">
+      <c r="M112" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="J115" s="41" t="n"/>
-      <c r="M115" t="inlineStr">
+      <c r="M115" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="J116" s="41" t="n"/>
-      <c r="M116" t="inlineStr">
+      <c r="M116" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="J119" s="41" t="n"/>
-      <c r="M119" t="inlineStr">
+      <c r="M119" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="J120" s="41" t="n"/>
-      <c r="M120" t="inlineStr">
+      <c r="M120" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -7786,7 +7786,7 @@
         </is>
       </c>
       <c r="J127" s="41" t="n"/>
-      <c r="M127" t="inlineStr">
+      <c r="M127" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="J134" s="41" t="n"/>
-      <c r="M134" t="inlineStr">
+      <c r="M134" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I138" s="41" t="n"/>
       <c r="J138" s="41" t="n"/>
-      <c r="L138" t="inlineStr">
+      <c r="L138" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -8293,12 +8293,12 @@
         </is>
       </c>
       <c r="J139" s="41" t="n"/>
-      <c r="L139" t="inlineStr">
+      <c r="L139" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
+      <c r="M139" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -8431,7 +8431,7 @@
         </is>
       </c>
       <c r="J142" s="41" t="n"/>
-      <c r="M142" t="inlineStr">
+      <c r="M142" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="J144" s="41" t="n"/>
-      <c r="M144" t="inlineStr">
+      <c r="M144" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="I147" s="41" t="n"/>
       <c r="J147" s="41" t="n"/>
-      <c r="M147" t="inlineStr">
+      <c r="M147" s="0" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="J155" s="41" t="n"/>
-      <c r="M155" t="inlineStr">
+      <c r="M155" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="J156" s="41" t="n"/>
-      <c r="M156" t="inlineStr">
+      <c r="M156" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="J157" s="41" t="n"/>
-      <c r="M157" t="inlineStr">
+      <c r="M157" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="J158" s="41" t="n"/>
-      <c r="M158" t="inlineStr">
+      <c r="M158" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="J164" s="41" t="n"/>
-      <c r="M164" t="inlineStr">
+      <c r="M164" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="J168" s="41" t="n"/>
-      <c r="M168" t="inlineStr">
+      <c r="M168" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="J169" s="41" t="n"/>
-      <c r="M169" t="inlineStr">
+      <c r="M169" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="J170" s="41" t="n"/>
-      <c r="M170" t="inlineStr">
+      <c r="M170" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="J171" s="41" t="n"/>
-      <c r="M171" t="inlineStr">
+      <c r="M171" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="J172" s="41" t="n"/>
-      <c r="M172" t="inlineStr">
+      <c r="M172" s="0" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
@@ -9776,7 +9776,7 @@
         </is>
       </c>
       <c r="J173" s="41" t="n"/>
-      <c r="M173" t="inlineStr">
+      <c r="M173" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="J177" s="41" t="n"/>
-      <c r="M177" t="inlineStr">
+      <c r="M177" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="J178" s="41" t="n"/>
-      <c r="M178" t="inlineStr">
+      <c r="M178" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -10043,12 +10043,12 @@
         </is>
       </c>
       <c r="J179" s="41" t="n"/>
-      <c r="L179" t="inlineStr">
+      <c r="L179" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
+      <c r="M179" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -10409,7 +10409,7 @@
         </is>
       </c>
       <c r="J188" s="41" t="n"/>
-      <c r="M188" t="inlineStr">
+      <c r="M188" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I191" s="41" t="n"/>
       <c r="J191" s="41" t="n"/>
-      <c r="L191" t="inlineStr">
+      <c r="L191" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="I193" s="41" t="n"/>
       <c r="J193" s="41" t="n"/>
-      <c r="L193" t="inlineStr">
+      <c r="L193" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="I199" s="41" t="n"/>
       <c r="J199" s="41" t="n"/>
-      <c r="L199" t="inlineStr">
+      <c r="L199" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -10913,7 +10913,7 @@
         </is>
       </c>
       <c r="J200" s="41" t="n"/>
-      <c r="M200" t="inlineStr">
+      <c r="M200" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I204" s="41" t="n"/>
       <c r="J204" s="41" t="n"/>
-      <c r="L204" t="inlineStr">
+      <c r="L204" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="J215" s="41" t="n"/>
-      <c r="M215" t="inlineStr">
+      <c r="M215" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -11520,7 +11520,7 @@
         </is>
       </c>
       <c r="J216" s="41" t="n"/>
-      <c r="M216" t="inlineStr">
+      <c r="M216" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="J217" s="41" t="n"/>
-      <c r="M217" t="inlineStr">
+      <c r="M217" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="J218" s="41" t="n"/>
-      <c r="M218" t="inlineStr">
+      <c r="M218" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="J219" s="41" t="n"/>
-      <c r="M219" t="inlineStr">
+      <c r="M219" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="J221" s="41" t="n"/>
-      <c r="M221" t="inlineStr">
+      <c r="M221" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="J231" s="41" t="n"/>
-      <c r="M231" t="inlineStr">
+      <c r="M231" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="I232" s="41" t="n"/>
       <c r="J232" s="41" t="n"/>
-      <c r="M232" t="inlineStr">
+      <c r="M232" s="0" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
@@ -12371,7 +12371,7 @@
         </is>
       </c>
       <c r="J238" s="41" t="n"/>
-      <c r="M238" t="inlineStr">
+      <c r="M238" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="J240" s="41" t="n"/>
-      <c r="M240" t="inlineStr">
+      <c r="M240" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="I241" s="41" t="n"/>
       <c r="J241" s="41" t="n"/>
-      <c r="L241" t="inlineStr">
+      <c r="L241" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="J243" s="41" t="n"/>
-      <c r="M243" t="inlineStr">
+      <c r="M243" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="J244" s="41" t="n"/>
-      <c r="M244" t="inlineStr">
+      <c r="M244" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12668,7 +12668,7 @@
         </is>
       </c>
       <c r="J245" s="41" t="n"/>
-      <c r="M245" t="inlineStr">
+      <c r="M245" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="J246" s="41" t="n"/>
-      <c r="M246" t="inlineStr">
+      <c r="M246" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="J247" s="41" t="n"/>
-      <c r="M247" t="inlineStr">
+      <c r="M247" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -13071,7 +13071,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr">
+      <c r="M255" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -13120,7 +13120,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr">
+      <c r="M256" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -13489,7 +13489,7 @@
           <t>live</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr">
+      <c r="M265" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -13702,7 +13702,7 @@
           <t>meta</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
+      <c r="M270" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -13955,7 +13955,7 @@
         </is>
       </c>
       <c r="J276" s="41" t="n"/>
-      <c r="M276" t="inlineStr">
+      <c r="M276" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="J281" s="41" t="n"/>
-      <c r="M281" t="inlineStr">
+      <c r="M281" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14213,7 +14213,7 @@
         </is>
       </c>
       <c r="J282" s="41" t="n"/>
-      <c r="M282" t="inlineStr">
+      <c r="M282" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14262,7 +14262,7 @@
         </is>
       </c>
       <c r="J283" s="41" t="n"/>
-      <c r="M283" t="inlineStr">
+      <c r="M283" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="J284" s="41" t="n"/>
-      <c r="M284" t="inlineStr">
+      <c r="M284" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14432,7 +14432,7 @@
         </is>
       </c>
       <c r="J287" s="41" t="n"/>
-      <c r="M287" t="inlineStr">
+      <c r="M287" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="J288" s="41" t="n"/>
-      <c r="M288" t="inlineStr">
+      <c r="M288" s="0" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="J291" s="41" t="n"/>
-      <c r="M291" t="inlineStr">
+      <c r="M291" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14699,7 +14699,7 @@
         </is>
       </c>
       <c r="J293" s="41" t="n"/>
-      <c r="M293" t="inlineStr">
+      <c r="M293" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14784,7 +14784,7 @@
         </is>
       </c>
       <c r="J295" s="41" t="n"/>
-      <c r="M295" t="inlineStr">
+      <c r="M295" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14833,7 +14833,7 @@
         </is>
       </c>
       <c r="J296" s="41" t="n"/>
-      <c r="M296" t="inlineStr">
+      <c r="M296" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="I297" s="41" t="n"/>
       <c r="J297" s="41" t="n"/>
-      <c r="L297" t="inlineStr">
+      <c r="L297" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="J299" s="41" t="n"/>
-      <c r="M299" t="inlineStr">
+      <c r="M299" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="J304" s="41" t="n"/>
-      <c r="M304" t="inlineStr">
+      <c r="M304" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15341,7 +15341,7 @@
         </is>
       </c>
       <c r="J309" s="41" t="n"/>
-      <c r="M309" t="inlineStr">
+      <c r="M309" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="J311" s="41" t="n"/>
-      <c r="M311" t="inlineStr">
+      <c r="M311" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15547,7 +15547,7 @@
         </is>
       </c>
       <c r="J314" s="41" t="n"/>
-      <c r="M314" t="inlineStr">
+      <c r="M314" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15596,7 +15596,7 @@
         </is>
       </c>
       <c r="J315" s="41" t="n"/>
-      <c r="M315" t="inlineStr">
+      <c r="M315" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="J318" s="41" t="n"/>
-      <c r="M318" t="inlineStr">
+      <c r="M318" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="I322" s="41" t="n"/>
       <c r="J322" s="41" t="n"/>
-      <c r="L322" t="inlineStr">
+      <c r="L322" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -16015,7 +16015,7 @@
         </is>
       </c>
       <c r="J326" s="41" t="n"/>
-      <c r="M326" t="inlineStr">
+      <c r="M326" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -16060,7 +16060,7 @@
         </is>
       </c>
       <c r="J327" s="41" t="n"/>
-      <c r="M327" t="inlineStr">
+      <c r="M327" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="J328" s="41" t="n"/>
-      <c r="M328" t="inlineStr">
+      <c r="M328" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="J331" s="41" t="n"/>
-      <c r="M331" t="inlineStr">
+      <c r="M331" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -16455,7 +16455,7 @@
         </is>
       </c>
       <c r="J337" s="41" t="n"/>
-      <c r="M337" t="inlineStr">
+      <c r="M337" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -16608,7 +16608,7 @@
         </is>
       </c>
       <c r="J341" s="41" t="n"/>
-      <c r="M341" t="inlineStr">
+      <c r="M341" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="J342" s="41" t="n"/>
-      <c r="M342" t="inlineStr">
+      <c r="M342" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -16770,7 +16770,7 @@
         </is>
       </c>
       <c r="J345" s="41" t="n"/>
-      <c r="M345" t="inlineStr">
+      <c r="M345" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="J354" s="41" t="n"/>
-      <c r="M354" t="inlineStr">
+      <c r="M354" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17304,7 +17304,7 @@
         </is>
       </c>
       <c r="J359" s="41" t="n"/>
-      <c r="M359" t="inlineStr">
+      <c r="M359" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="J360" s="41" t="n"/>
-      <c r="M360" t="inlineStr">
+      <c r="M360" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17402,7 +17402,7 @@
         </is>
       </c>
       <c r="J361" s="41" t="n"/>
-      <c r="M361" t="inlineStr">
+      <c r="M361" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="J362" s="41" t="n"/>
-      <c r="M362" t="inlineStr">
+      <c r="M362" s="0" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
@@ -17496,7 +17496,7 @@
         </is>
       </c>
       <c r="J363" s="41" t="n"/>
-      <c r="M363" t="inlineStr">
+      <c r="M363" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17537,7 +17537,7 @@
         </is>
       </c>
       <c r="J364" s="41" t="n"/>
-      <c r="M364" t="inlineStr">
+      <c r="M364" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17582,7 +17582,7 @@
         </is>
       </c>
       <c r="J365" s="41" t="n"/>
-      <c r="M365" t="inlineStr">
+      <c r="M365" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17627,7 +17627,7 @@
         </is>
       </c>
       <c r="J366" s="41" t="n"/>
-      <c r="M366" t="inlineStr">
+      <c r="M366" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17672,7 +17672,7 @@
         </is>
       </c>
       <c r="J367" s="41" t="n"/>
-      <c r="M367" t="inlineStr">
+      <c r="M367" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="I368" s="41" t="n"/>
       <c r="J368" s="41" t="n"/>
-      <c r="M368" t="inlineStr">
+      <c r="M368" s="0" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
@@ -18054,12 +18054,12 @@
         </is>
       </c>
       <c r="J377" s="41" t="n"/>
-      <c r="L377" t="inlineStr">
+      <c r="L377" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr">
+      <c r="M377" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="I379" s="41" t="n"/>
       <c r="J379" s="41" t="n"/>
-      <c r="M379" t="inlineStr">
+      <c r="M379" s="0" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
@@ -18181,7 +18181,7 @@
         </is>
       </c>
       <c r="J380" s="41" t="n"/>
-      <c r="M380" t="inlineStr">
+      <c r="M380" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -18498,7 +18498,7 @@
         </is>
       </c>
       <c r="J388" s="41" t="n"/>
-      <c r="M388" t="inlineStr">
+      <c r="M388" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -18583,7 +18583,7 @@
         </is>
       </c>
       <c r="J390" s="41" t="n"/>
-      <c r="M390" t="inlineStr">
+      <c r="M390" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -18632,7 +18632,7 @@
         </is>
       </c>
       <c r="J391" s="41" t="n"/>
-      <c r="M391" t="inlineStr">
+      <c r="M391" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -18965,7 +18965,7 @@
         </is>
       </c>
       <c r="J400" s="41" t="n"/>
-      <c r="M400" t="inlineStr">
+      <c r="M400" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -19006,7 +19006,7 @@
       </c>
       <c r="I401" s="41" t="n"/>
       <c r="J401" s="41" t="n"/>
-      <c r="L401" t="inlineStr">
+      <c r="L401" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
@@ -19051,12 +19051,12 @@
         </is>
       </c>
       <c r="J402" s="41" t="n"/>
-      <c r="L402" t="inlineStr">
+      <c r="L402" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr">
+      <c r="M402" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -19173,7 +19173,58 @@
         </is>
       </c>
     </row>
-    <row r="406" ht="15.75" customHeight="1" s="39"/>
+    <row r="406" ht="15.75" customHeight="1" s="39">
+      <c r="A406" s="0" t="inlineStr">
+        <is>
+          <t>Entanglement</t>
+        </is>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="C406" s="0" t="inlineStr">
+        <is>
+          <t>Monogamy in CKW form</t>
+        </is>
+      </c>
+      <c r="D406" s="0" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
+      <c r="F406" s="0" t="inlineStr">
+        <is>
+          <t>Grounded - consistent with, not forced by (re-tiered 2026-09-04, was form D)</t>
+        </is>
+      </c>
+      <c r="G406" s="0" t="inlineStr">
+        <is>
+          <t>the budget gives a CONSTANT bound, CKW's is STATE-DEPENDENT; general measure-saturation would close the gap but yields EQUALITY, losing the strict inequality and the residual three-tangle. Open item O-SubAdd (065 6.x)</t>
+        </is>
+      </c>
+      <c r="H406" s="0" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="J406" s="0" t="inlineStr">
+        <is>
+          <t>P-V5-Budget, P-Measure-Saturation</t>
+        </is>
+      </c>
+      <c r="K406" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#124), read against the paper's own audit table. NEW ROW 2026-09-06, mirroring the split the entanglement arc ledger made on 2026-09-04 and the sheet never picked up. Appended rather than inserted so no existing row number moves. DISCREPANCY TO RECONCILE: Paper_065's audit table row 8 labels this step 'A -&gt; consistency'; the arc ledger's claim row calls it 'Grounded - consistent with, not forced by'. Tiered here to the arc ledger; the paper's step-level label is weaker.</t>
+        </is>
+      </c>
+      <c r="M406" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
     <row r="407" ht="15.75" customHeight="1" s="39"/>
     <row r="408" ht="15.75" customHeight="1" s="39"/>
     <row r="409" ht="15.75" customHeight="1" s="39"/>
@@ -24229,7 +24280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="39" min="1" max="1"/>
@@ -24310,7 +24361,7 @@
         </is>
       </c>
       <c r="E3" s="41" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -24333,7 +24384,7 @@
         </is>
       </c>
       <c r="E4" s="41" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -24356,7 +24407,7 @@
         </is>
       </c>
       <c r="E5" s="41" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
@@ -24425,7 +24476,7 @@
         </is>
       </c>
       <c r="E8" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -24494,7 +24545,7 @@
         </is>
       </c>
       <c r="E11" s="41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -24540,7 +24591,7 @@
         </is>
       </c>
       <c r="E13" s="41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -24586,7 +24637,7 @@
         </is>
       </c>
       <c r="E15" s="41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -24655,7 +24706,7 @@
         </is>
       </c>
       <c r="E18" s="41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -24705,7 +24756,18 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="39"/>
-    <row r="22" ht="15.75" customHeight="1" s="39"/>
+    <row r="22" ht="15.75" customHeight="1" s="39">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WARNING - 2026-09-06</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>'Derived' does NOT mean here what it means in the per-folder *_TieredClaims_Ledger.md files this workbook is fed by. Those head their top section 'Derived (forced - but each CONDITIONAL ON A POSTULATE in the Postulated table)' (entanglement), '(conditioning postulate noted)' (gravity), '(conditional on the named postulate)' (qft), '(conditional on the 13 postulated primitives)' (q-compute). Here Derived means NO paper-specific postulate. Copying a claim from an arc ledger's Derived section straight into this Tier column OVER-PROMOTES it - the qualifier lives in the parenthetical and the parenthetical does not travel. That is the root cause of the C4 flags. When transcribing, read the ledger row's 'Inherited / open' cell, not the section heading: if it names a postulate, the tier here is Grounded or Postulated.</t>
+        </is>
+      </c>
+    </row>
     <row r="23" ht="15.75" customHeight="1" s="39"/>
     <row r="24" ht="15.75" customHeight="1" s="39"/>
     <row r="25" ht="15.75" customHeight="1" s="39"/>
@@ -25710,7 +25772,7 @@
         </is>
       </c>
       <c r="B2" s="34" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -25740,7 +25802,7 @@
         </is>
       </c>
       <c r="B5" s="34" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -25760,7 +25822,7 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -25900,7 +25962,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="45.14" customWidth="1" style="39" min="1" max="1"/>
@@ -26059,14 +26121,12 @@
           <t>Mechanical census, same date</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="B13" s="0" t="n">
+        <v>174</v>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>Distinctly-named P-* postulates across physics-papers/ (7 further matches merged as spelling variants), so the declared set is 13 primitives + 173 = 186. Re-runnable: internal notes/_census_postulates.py, which exits nonzero when the count drifts from its baseline. Paper_088 stated 31 and Paper_087 §4.15 ~35; both now carry dated census notes. Paper_100's '60+' is the least wrong figure in the corpus.</t>
+          <t>Distinctly-named P-* postulates across physics-papers/ (re-run 2026-09-06)</t>
         </is>
       </c>
     </row>
@@ -26106,11 +26166,11 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>+13 primitives = 184. Every named commitment in physics-papers/, incl. one-off modelling choices</t>
+          <t>+13 primitives = 187</t>
         </is>
       </c>
     </row>
@@ -26121,11 +26181,11 @@
         </is>
       </c>
       <c r="B18" s="0" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>+13 = 81. The commitment outlives the derivation that introduced it</t>
+          <t>+13 = 95</t>
         </is>
       </c>
     </row>
@@ -26136,11 +26196,11 @@
         </is>
       </c>
       <c r="B19" s="0" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>+13 = 56</t>
+          <t>+13 = 65</t>
         </is>
       </c>
     </row>
@@ -26151,11 +26211,11 @@
         </is>
       </c>
       <c r="B20" s="0" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>+13 = 39. The framework's standing commitments. This is the row to quote for parsimony</t>
+          <t>+13 = 45. The framework's standing commitments. This is the row to quote for parsimony</t>
         </is>
       </c>
     </row>
@@ -26166,11 +26226,11 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>+13 = 27. THIS workbook's basis — the 'live' flag in Claims col J</t>
+          <t>+13 = 28. THIS workbook's basis - the 'live' flag in the Postulate column</t>
         </is>
       </c>
     </row>
@@ -26181,11 +26241,11 @@
         </is>
       </c>
       <c r="B22" s="0" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>60% of the total. Local modelling choices, scoped to a single derivation, like a gauge choice</t>
+          <t>51% of the total (was 60% on 2026-09-04). Local modelling choices, scoped to a single derivation</t>
         </is>
       </c>
     </row>
@@ -26199,6 +26259,18 @@
       <c r="C23" s="0" t="inlineStr">
         <is>
           <t>Quote the LADDER, not a number. Both the honest large figure (171) and the honest small one (26) belong in public material; either alone misleads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>LADDER REFRESHED 2026-09-06</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>Re-derived with `python "internal notes/_census_postulates.py" --triage`. The 2026-09-04 figures were low across every rung; cross-cutting (&gt;=4 papers) moved 26 -&gt; 32 and the one-off share fell 60% -&gt; 51%, so the sheet was UNDERSTATING the shared-commitment case, not overstating it.</t>
         </is>
       </c>
     </row>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -3839,7 +3839,7 @@
       <c r="J42" s="41" t="n"/>
       <c r="K42" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Constants_Ledger_and_G_Dimension.md declares P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>Nothing beyond P01-P13 and standard math. VERIFIED 2026-09-06 (#125). C4 FALSE POSITIVE: the flag came from P-RB-1, which the source file attaches to a DIFFERENT claim, the constants ledger (sheet row 96, already Grounded). This row is dimensional analysis, and the source calls it derived in its own words. One caveat the source records: whether Paper_027's d-dimensional derivation adds a dimensionless d-dependent factor is OPEN, though it should not change the power result.</t>
         </is>
       </c>
       <c r="M42" s="0" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D43" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E43" s="41" t="n"/>
@@ -3893,7 +3893,7 @@
       <c r="J43" s="41" t="n"/>
       <c r="K43" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_ED_Baryogenesis.md declares P-BinaryAdmission. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
+          <t>Nothing beyond the primitives, but the values are inherited. VERIFIED 2026-09-06 (#125). The row's own cell labels the derivation D-via-I; eta_B ~ 6e-10 is inherited (Planck/BBN) and WHICH chirality wins is IC-inherited.</t>
         </is>
       </c>
       <c r="M43" s="0" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D44" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E44" s="41" t="n"/>
@@ -3943,7 +3943,7 @@
       <c r="J44" s="41" t="n"/>
       <c r="K44" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_ED_Cos_06_InflationarySpectrum.md declares P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>Nothing beyond the primitives; the n_T = -r/8 consistency relation inherited. VERIFIED 2026-09-06 (#125). The row's own cell labels the cross-arc identification D-via-I.</t>
         </is>
       </c>
     </row>
@@ -3960,28 +3960,28 @@
       </c>
       <c r="C45" s="41" t="inlineStr">
         <is>
-          <t>a0 = cH0/(2pi), parameter-free ~10% match</t>
+          <t>a0 = cH0/(2pi): the SCALE ~cH0 is derived; the 1/(2pi) COEFFICIENT is postulated/disputed. ~10% match</t>
         </is>
       </c>
       <c r="D45" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Postulated</t>
         </is>
       </c>
       <c r="E45" s="41" t="n"/>
       <c r="F45" s="41" t="inlineStr">
         <is>
-          <t>2pi from azimuthal-Fourier normalization of the dipole projection</t>
+          <t>scale ~cH0 = D (Paper_029 audit row 12, reached three independent ways); the 2pi is NOT (audit rows 8, 10, 11)</t>
         </is>
       </c>
       <c r="G45" s="41" t="inlineStr">
         <is>
-          <t>~10% POSTDICTION; a0 value inherited via H0</t>
+          <t>a0 value inherited via H0; ~10% POSTDICTION; coefficient DISPUTED (gravity Staleness #10)</t>
         </is>
       </c>
       <c r="H45" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>CORRECTED 2026-09-06 - was Derived, and the claim text read parameter-free</t>
         </is>
       </c>
       <c r="I45" s="41" t="inlineStr">
@@ -3992,7 +3992,7 @@
       <c r="J45" s="41" t="n"/>
       <c r="K45" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_029_a0.md declares P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P (normalization choice) at Paper_029 audit rows 6 and 10, plus an A row at 5. VERIFIED 2026-09-06 (#125). THE SHEET WAS ASSERTING WHAT THE PAPER SUSPENDED. Paper_029's audit re-tiers a0 = cH0/(2pi) to Postulated / disputed (was D form-forced) at row 11, gives verdict A-position / M3 at row 15, and states that what is suspended is the coefficient, rows 8/10/11, and with it the NO FREE PARAMETER claim of section 5.3 - while this row's claim text read parameter-free. Audit row 10 is a P that must both erase the 2/3 the integral produces AND supply a 1/(2pi) the same integral cancelled. THE CORRECTION WAS ALREADY MADE ON 2026-09-04 and reached sheet row 20 and Core Predictions rows 3 and 19; it did not reach this row or row 342. A partial propagation, not a missed finding. WHAT SURVIVES: the scale a0 ~ cH0 is D by three independent routes (audit row 12), and a0(z) with exponent exactly 1 is D and EXPLICITLY INDEPENDENT of the coefficient dispute (audit row 14), so the flagship evolution bet is untouched.</t>
         </is>
       </c>
       <c r="M45" s="0" t="inlineStr">
@@ -4050,7 +4050,7 @@
       <c r="J46" s="41" t="n"/>
       <c r="K46" s="0" t="inlineStr">
         <is>
-          <t>none found - Paper_ED_DarkSector.md declares no censused postulate (mechanical check only, 2026-09-06; resolved ALIAS)</t>
+          <t>VERIFIED 2026-09-06 (#125). LEFT AT Derived DELIBERATELY. The formula embeds the disputed 1/(2pi), but Paper_029's audit row 14 states the EVOLUTION with exponent exactly 1 is D and independent of the coefficient dispute. The evolution is what this row claims. Flagged so the 2pi inside the formula is not read as settled.</t>
         </is>
       </c>
       <c r="M46" s="0" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D54" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E54" s="41" t="n"/>
@@ -4451,7 +4451,7 @@
       <c r="J54" s="41" t="n"/>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_089_V1Kernel.md declares P-NoBackwardChain, P-SubstrateLocality. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P-SubstrateLocality. VERIFIED 2026-09-06 (#125). The row's own cell already read: leans on an explicit P-SubstrateLocality postulate.</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="D55" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E55" s="41" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="J55" s="41" t="n"/>
       <c r="K55" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_089_V1Kernel.md, Paper_093_KernelArrow_of_Time.md declares P-NoBackwardChain, P-SubstrateLocality, P-T18-Arrow-Inheritance, P-T18-Kernel-Retardation. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>P-NoBackwardChain, plus a substrate-operational (not algebraic) closure. VERIFIED 2026-09-06 (#125). The row's own cell already recorded M2, and that upgrading to M1 needs P11 from a deeper layer (OPEN).</t>
         </is>
       </c>
       <c r="M55" s="0" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D56" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Asserted</t>
         </is>
       </c>
       <c r="E56" s="41" t="n"/>
@@ -4550,7 +4550,7 @@
       <c r="J56" s="41" t="n"/>
       <c r="K56" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_089_V1Kernel.md, Paper_093_KernelArrow_of_Time.md declares P-NoBackwardChain, P-SubstrateLocality, P-T18-Arrow-Inheritance, P-T18-Kernel-Retardation. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>Nothing beyond a stated position. VERIFIED 2026-09-06 (#125). The row's own Derived cell reads literally 'position' - the paper's A-position label - while the Tier column read Derived. Self-contradicting on its face, exactly like row 69 was.</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="D57" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E57" s="41" t="n"/>
@@ -4595,7 +4595,7 @@
       <c r="J57" s="41" t="n"/>
       <c r="K57" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_090_V5Kernel.md, Paper_094_ForwardCausality.md declares P-Causality-Propagation, P-Primitive-Forward-Causality. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>P-Causality-Propagation. VERIFIED 2026-09-06 (#125). The row's own cell read: inheritance postulated (P-Causality-Propagation); specific arrow derivations OPEN.</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D58" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E58" s="41" t="n"/>
@@ -4640,7 +4640,7 @@
       <c r="J58" s="41" t="n"/>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_025_HolographicBound.md declares P-Codim-1, P-Sat. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P-Codim-1, P-Sat; l_ED value inherited. VERIFIED 2026-09-06 (#125).</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="D59" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E59" s="41" t="n"/>
@@ -4685,7 +4685,7 @@
       <c r="J59" s="41" t="n"/>
       <c r="K59" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_026_CumulativeStrain.md declares P-Codim-1, P-Potential-Reading, P-Sat. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P-Potential-Reading (Model A); V1 1/R envelope inherited via DCGT. VERIFIED 2026-09-06 (#125).</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E60" s="41" t="n"/>
@@ -4730,7 +4730,7 @@
       <c r="J60" s="41" t="n"/>
       <c r="K60" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_032_5_FreeChainGeodesics.md declares P-FreeChain. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>P-FreeChain, plus the Paper_035 guardrails. VERIFIED 2026-09-06 (#125). The row's own cell read FORCED-CONDITIONAL on P-FreeChain, flagged the eikonal-to-action step OPEN, and recorded verdict M3, the weakest of the three. Arguably weaker than Grounded.</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D61" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E61" s="41" t="n"/>
@@ -4775,7 +4775,7 @@
       <c r="J61" s="41" t="n"/>
       <c r="K61" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_034_DeepMOND.md, Paper_036_MOND_FieldEquation.md declares P-Codim-1, P-MOND-Field-Form, P-MOND-Interpolation, P-No-New-Primitive. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved ALIAS)</t>
+          <t>P-MOND-Interpolation, P-MOND-Field-Form; the mu form inherited empirically. VERIFIED 2026-09-06 (#125). The row's own cell read FORM-FORCED GIVEN those two postulates.</t>
         </is>
       </c>
       <c r="M61" s="0" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="D62" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E62" s="41" t="n"/>
@@ -4825,7 +4825,7 @@
       <c r="J62" s="41" t="n"/>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_037_a0_Invariance.md declares P-H0-Cosmological-Invariant, P-Profile-Rescaling, P-RB-1, P-Substrate-c-Constancy. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P-H0-Cosmological-Invariant. VERIFIED 2026-09-06 (#125).</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       <c r="J70" s="41" t="n"/>
       <c r="K70" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_GR-III_DynamicalRule.md declares P-Commitment-Linear. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>Nothing beyond P01-P13. VERIFIED 2026-09-06 (#125). C4 FALSE POSITIVE: GR-III declares P-Commitment-Linear, but that postulate carries row 69 (alpha=1), not this claim. GR-III's audit labels c_s = c a plain D (leading order), with the reserve-dissipative step structural + measured. This is one of the six rows #122 explicitly declined to claim either way; it stands.</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="D76" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E76" s="41" t="n"/>
@@ -5486,7 +5486,7 @@
       <c r="J76" s="41" t="n"/>
       <c r="K76" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_058b_PlateauDomain_AlphaTopological.md declares P-Corr-Budget, P-QD-LiveWeight, P-Redundancy-Mapping. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
+          <t>P-Corr-Budget (Paper_058), plus the row's own conditional on three inherited/QI rows. VERIFIED 2026-09-06 (#125).</t>
         </is>
       </c>
       <c r="M76" s="0" t="inlineStr">
@@ -5532,7 +5532,7 @@
       <c r="J77" s="41" t="n"/>
       <c r="K77" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_058b_PlateauDomain_AlphaTopological.md declares P-Corr-Budget, P-QD-LiveWeight, P-Redundancy-Mapping. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
+          <t>Nothing beyond P01-P13, via the QuantumDarwinism accounting theorem (sheet row 95, which also stands). VERIFIED 2026-09-06 (#125). C4 FALSE POSITIVE: Paper_058b declares P-Corr-Budget, which carries row 76, not this claim.</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D78" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E78" s="41" t="n"/>
@@ -5577,7 +5577,7 @@
       <c r="J78" s="41" t="n"/>
       <c r="K78" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_016_MinimalCoupling.md declares P-Bundle-Definition, P-Connection-Naming, P-Fiber-Naming, P-NonAbelian-Analogy. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P-Polarity-Connection-Match. VERIFIED 2026-09-06 (#125). The postulate was sitting in the row's own Derived cell (DCGT coarse-graining + P-Polarity-Connection-Match), not in the Postulate column.</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E79" s="41" t="n"/>
@@ -5618,7 +5618,7 @@
       <c r="J79" s="41" t="n"/>
       <c r="K79" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_017_FreeScalarQFT.md declares P-Lorentz-Covariant-Continuum, P-Scalar-Match. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P-Scalar-Match and P-Lorentz-Covariant-Continuum. VERIFIED 2026-09-06 (#125). Paper_017's audit labels this step D, but the object it is about, the continuum free-scalar equation, is built by that same audit as a P (definitional construction) under P-Scalar-Match plus P-Lorentz-Covariant-Continuum. A covariance claim cannot outrank the equation it is about. NOTE: P-Lorentz-Covariant-Continuum was relabelled D to P in round 8 to fix a Paper_073 / Paper_017 inconsistency, and the sheet never picked that up.</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E82" s="41" t="n"/>
@@ -5762,7 +5762,7 @@
       <c r="J82" s="41" t="n"/>
       <c r="K82" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_022_YM5_GaugeQuotient.md declares P-Gauge-Orbit-Non-Empty, P-Quotient-Hilbert. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>Nothing beyond the primitives; fiber-bundle quotient and DCGT composed. VERIFIED 2026-09-06 (#125). The row's own cell reads D-via-I. Constructive Gribov resolution remains OPEN.</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E83" s="41" t="n"/>
@@ -5807,7 +5807,7 @@
       <c r="J83" s="41" t="n"/>
       <c r="K83" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_024_LindbladLimit.md declares P-Factorized-IC, P-Markovian, P-Weak-Coupling. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>Nothing beyond the primitives; specific L_k and rates inherited. VERIFIED 2026-09-06 (#125). The row's own cell reads FORM-FORCED as the Markovian limit (D-via-I). Non-Markovian OPEN.</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E85" s="41" t="n"/>
@@ -5910,7 +5910,7 @@
       <c r="J85" s="41" t="n"/>
       <c r="K85" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_001_PreIndividuation.md declares P-LinRate, P-RB-1. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>P (convention): the square-root-amplitude convention; P (definition): arg(P_K) = pi_K. VERIFIED 2026-09-06 (#125). Paper_001's audit gives each of these its own P row. The sqrt convention is a paper-specific CHOICE (the alternative would give a different relationship to the Born rule), not one of the 13 primitives. The sheet's own cell already read: sqrt-convention + arg=pi_K = P.</t>
         </is>
       </c>
       <c r="M85" s="0" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E86" s="41" t="n"/>
@@ -5960,7 +5960,7 @@
       <c r="J86" s="41" t="n"/>
       <c r="K86" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_009_BerryPhase.md declares P-Adiabatic-Coarse-Graining, P-Loop-Closure. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>Nothing beyond the primitives; numerical gamma_C inherited. VERIFIED 2026-09-06 (#125). The row's own cell reads D-via-I. UPSTREAM CAVEAT: the holonomy is taken on Paper_016's connection, which row 78 now shows rests on P-Polarity-Connection-Match. If that load propagates, this is Grounded rather than D-via-I. Flagged, not decided.</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E87" s="41" t="n"/>
@@ -6005,7 +6005,7 @@
       <c r="J87" s="41" t="n"/>
       <c r="K87" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_010_AharonovBohm.md declares P-Excluded-Region, P-Flat-Outside. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>Nothing beyond the primitives; e/hbar inherited. VERIFIED 2026-09-06 (#125). The row's own cell reads D-via-I, and the paper states plainly that ED does NOT newly predict AB. Same upstream caveat as row 86.</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>D-via-I / Form-forced</t>
         </is>
       </c>
       <c r="E88" s="41" t="n"/>
@@ -6050,7 +6050,7 @@
       <c r="J88" s="41" t="n"/>
       <c r="K88" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_011_BlochTheorem.md declares P-Discrete-Translation, P-Symmetric-Hamiltonian. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved EXACT)</t>
+          <t>Nothing beyond the primitives; band content inherited. VERIFIED 2026-09-06 (#125). The row's own cell reads D-via-I (abelian rep theory).</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       <c r="J95" s="41" t="n"/>
       <c r="K95" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - Paper_QuantumDarwinism_RecordBandwidth.md declares P-QD-LiveWeight, P-V5-Budget. Whether THIS claim needs it is UNREAD; a human must check. (C4 flag, 2026-09-06; resolved FUZZY)</t>
+          <t>Nothing beyond P01-P13; absolute W_max inherited. VERIFIED 2026-09-06 (#125). C4 FALSE POSITIVE: the paper declares P-QD-LiveWeight, but its audit attaches that to the GHZ-width ceiling, a different claim. The accounting theorem and the unbounded-redundancy corollary are labelled D-structural and D. NOTE the label is D-structural, not plain D.</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16639,7 @@
       <c r="F342" s="41" t="n"/>
       <c r="G342" s="41" t="inlineStr">
         <is>
-          <t>form-derived, ~10% parameter-free match; H0 INHERITED; 029's reading is STATIC ('tracks whichever H0') — no a0(z) (Staleness #1)</t>
+          <t>SCALE form-derived, ~10% match; the 1/(2pi) COEFFICIENT postulated/disputed (2026-09-04); H0 INHERITED; 029's reading is STATIC (tracks whichever H0)</t>
         </is>
       </c>
       <c r="H342" s="41" t="inlineStr">
@@ -16653,6 +16653,11 @@
         </is>
       </c>
       <c r="J342" s="41" t="n"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#125). STALE WORDING CORRECTED 2026-09-06: this cell read 'form-derived, ~10% parameter-free match'. Same partial propagation as row 45.</t>
+        </is>
+      </c>
       <c r="M342" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -24361,7 +24366,7 @@
         </is>
       </c>
       <c r="E3" s="41" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -24384,7 +24389,7 @@
         </is>
       </c>
       <c r="E4" s="41" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -24407,7 +24412,7 @@
         </is>
       </c>
       <c r="E5" s="41" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
@@ -24591,7 +24596,7 @@
         </is>
       </c>
       <c r="E13" s="41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -24614,7 +24619,7 @@
         </is>
       </c>
       <c r="E14" s="41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -24757,12 +24762,12 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" s="39"/>
     <row r="22" ht="15.75" customHeight="1" s="39">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>WARNING - 2026-09-06</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>'Derived' does NOT mean here what it means in the per-folder *_TieredClaims_Ledger.md files this workbook is fed by. Those head their top section 'Derived (forced - but each CONDITIONAL ON A POSTULATE in the Postulated table)' (entanglement), '(conditioning postulate noted)' (gravity), '(conditional on the named postulate)' (qft), '(conditional on the 13 postulated primitives)' (q-compute). Here Derived means NO paper-specific postulate. Copying a claim from an arc ledger's Derived section straight into this Tier column OVER-PROMOTES it - the qualifier lives in the parenthetical and the parenthetical does not travel. That is the root cause of the C4 flags. When transcribing, read the ledger row's 'Inherited / open' cell, not the section heading: if it names a postulate, the tier here is Grounded or Postulated.</t>
         </is>
@@ -25759,12 +25764,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="43.43" customWidth="1" style="39" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -25772,7 +25778,7 @@
         </is>
       </c>
       <c r="B2" s="34" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -25802,7 +25808,7 @@
         </is>
       </c>
       <c r="B5" s="34" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -25822,7 +25828,7 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -25832,7 +25838,7 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -1524,6 +1524,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
@@ -2115,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M406"/>
+  <dimension ref="A1:M407"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="39" min="1" max="1"/>
@@ -7145,6 +7146,11 @@
         </is>
       </c>
       <c r="J112" s="41" t="n"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). CHECKED, CLEAN. gravity #29 (2026-09-04) fixed a cross-arc tier disagreement on c_T = c (D-structural in gravity, Inherited in dynamics). This row already reads 'speed=c ... all INHERITED', which is the side the fix landed on. No change.</t>
+        </is>
+      </c>
       <c r="M112" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -7448,6 +7454,11 @@
         </is>
       </c>
       <c r="J119" s="41" t="n"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). CHECKED, CLEAN. gravity #24 (2026-09-04) audited Paper_038_5 and found 'the paper is honest, the README is not'; the force-vs-stipulate residual was confirmed and makes the MEMORY pointer stale, not section 3.5. This row already carries that residual in its own Inherited/Open cell. No change.</t>
+        </is>
+      </c>
       <c r="M119" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -7497,6 +7508,11 @@
         </is>
       </c>
       <c r="J120" s="41" t="n"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). FLAGGED, NOT RE-TIERED - this needs the author, not me. gravity #19 (2026-09-04) found that Paper_KM-I and Paper_030 handle the HIGH-acceleration limit by two different and incompatible mechanisms, and neither cites the other's: Paper_030 section 7.1 uses a SWITCH (three regimes, P14 inactive above a0), while KM-I uses a smooth Cassini-constrained family - which is what this row's own Inherited/Open cell records. #19 is explicit that THE FINDING IS NOT IN KM-I: KM-I is careful, labels its hinge D conditional on I-030, and says outright that it carries Paper_030's law rather than re-deriving it. But #19 also says an earlier item 'named the wrong one as standing', and #34 (2026-09-04) subsequently DERIVED the switch. This row's Status still reads 'THE STANDING MOND RESULT' with no record of that tension. The claim itself is not disputed and KM-I is not falsified.</t>
+        </is>
+      </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -10043,6 +10059,11 @@
         </is>
       </c>
       <c r="J179" s="41" t="n"/>
+      <c r="K179" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). CHECKED, NO CHANGE NEEDED to the tier. This row is the ANALYTIC claim - Coh is maximal at alignment by the 1.3 formula - which is form-forced-conditional and untouched by #112. Its Status line 'sign supplied at Measured tier' now points at row 199, whose measured object is Grad; #112 item 2 confirms the sign transfers between them.</t>
+        </is>
+      </c>
       <c r="L179" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
@@ -10508,7 +10529,7 @@
       </c>
       <c r="C191" s="41" t="inlineStr">
         <is>
-          <t>Phase-coherence constructive sign supplied (P12-Coh rewards alignment)</t>
+          <t>Phase-coherence constructive sign supplied (alignment is rewarded; +Coh and -Grad both do it)</t>
         </is>
       </c>
       <c r="D191" s="41" t="inlineStr">
@@ -10519,21 +10540,26 @@
       <c r="E191" s="41" t="n"/>
       <c r="F191" s="41" t="inlineStr">
         <is>
-          <t>build-verified 2D/3D; finite-reach not crystalline</t>
+          <t>build-verified 2D/3D on Grad intensively scored; not crystalline on ALL THREE functionals (ten seeds, 0/10)</t>
         </is>
       </c>
       <c r="G191" s="41" t="inlineStr">
         <is>
-          <t>conditional on P12-Coh operationalization</t>
+          <t>the SIGN transfers from the P12-Coh paper; the build behind it measured Grad, not Coh</t>
         </is>
       </c>
       <c r="H191" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>CORRECTED 2026-09-06 - claim read '(P12-Coh rewards alignment)' and 'conditional on P12-Coh operationalization'</t>
         </is>
       </c>
       <c r="I191" s="41" t="n"/>
       <c r="J191" s="41" t="n"/>
+      <c r="K191" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). OVERTAKEN by gravity ledger #112 (2026-09-06): Paper_PhaseCoherence_P12Coh states the Coh formula at 1.3 but its build implements v3_active = |acc|/n, which carries no neighbour-neighbour cross term and is therefore Grad's phase half scored intensively. WHAT SURVIVES for this row, per #112 item 2: the constructive SIGN transfers, because +Coh and -Grad both reward alignment and differ only by the NN term - so QuadraticStrain's MOND interference term keeps the sign the paper was written to supply. And per item 1 the no-crystal result holds for the stated Coh formula too, re-run on ten seeds across all three functionals. Only the word 'build-verified' had to move from Coh to Grad.</t>
+        </is>
+      </c>
       <c r="L191" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
@@ -10838,7 +10864,7 @@
       </c>
       <c r="C199" s="41" t="inlineStr">
         <is>
-          <t>P12 coherence rewards alignment but stays FINITE-REACH (no crystal) 2D+3D; V5's attractive local-lock from P12's positive sign (flip destroys it)</t>
+          <t>Alignment is rewarded and reach stays FINITE (no crystal) 2D+3D; V5's attractive local-lock from P12's positive sign (flip destroys it). MEASURED ON GRAD INTENSIVELY SCORED, not on canonical Coh</t>
         </is>
       </c>
       <c r="D199" s="41" t="inlineStr">
@@ -10849,21 +10875,26 @@
       <c r="E199" s="41" t="n"/>
       <c r="F199" s="41" t="inlineStr">
         <is>
-          <t>trivial connection crystallizes (R=1); disorder+irreversibility =&gt; xi few lattice units; within-cluster spread ~0.27x at finite reach</t>
+          <t>trivial connection crystallizes (R=1); disorder+irreversibility =&gt; xi a few lattice units; within-cluster spread ~0.27x at finite reach - all on Grad intensively scored</t>
         </is>
       </c>
       <c r="G199" s="41" t="inlineStr">
         <is>
-          <t>reach xi value-inherited; V5 existence stays a P10 posit</t>
+          <t>reach xi value-inherited AND functional-dependent; V5 existence stays a P10 posit; canonical Coh shows NO alignment gain under any normalization tried (#111), so the finite-reach result does not transfer to it</t>
         </is>
       </c>
       <c r="H199" s="41" t="inlineStr">
         <is>
-          <t>current — Measured (supplies the attractive/constructive sign)</t>
+          <t>CORRECTED 2026-09-06 - read 'P12 coherence rewards alignment but stays FINITE-REACH'; the measured object is Grad</t>
         </is>
       </c>
       <c r="I199" s="41" t="n"/>
       <c r="J199" s="41" t="n"/>
+      <c r="K199" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). OVERTAKEN by gravity ledger #112 and #111 (2026-09-06). This is the row where the correction BITES rather than transferring. #112 item 3: the finite-reach result and the measured xi are properties of Grad intensively scored; canonical Coh was tested directly and shows no alignment gain under any normalization, because its neighbour-neighbour term does not contain the candidate's own phase. The no-crystal half DOES hold for canonical Coh (#112 item 1, ten seeds, 0/10 crystal, R about 0.01-0.07 against R &gt; 0.8 for a crystal verdict). CALIBRATION: absolute xi values are measured at rho* = 0.5 and increment = 1, both undocumented (#119, #121); the ranking of arms is stable across both but the binding threshold is not.</t>
+        </is>
+      </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
           <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
@@ -12553,7 +12584,7 @@
       </c>
       <c r="D243" s="41" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Superseded</t>
         </is>
       </c>
       <c r="E243" s="41" t="n"/>
@@ -12565,7 +12596,7 @@
       </c>
       <c r="H243" s="41" t="inlineStr">
         <is>
-          <t>open (stale)</t>
+          <t>SUPERSEDED - re-tiered from Open 2026-09-06</t>
         </is>
       </c>
       <c r="I243" s="41" t="inlineStr">
@@ -12574,6 +12605,11 @@
         </is>
       </c>
       <c r="J243" s="41" t="n"/>
+      <c r="K243" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). OVERTAKEN, and the sheet had already diagnosed it without acting: this row's own Inherited/Open cell reads 'STALE framing ... SUPERSEDED by the reconstruction (next row)' and its Status read 'open (stale)', while the Tier stayed Open. Row 244 carries the current state - orthogonality REDUCED, C selected, residual = Soler - and row 178 says the status is 'reduced to the Soler residual', NOT 'blocking / three routes fail'. Re-tiered Open -&gt; Superseded. This is exactly the stale-status class CLAUDE.md names: Paper_004's 2026-07-02 'three routes fail' wording predates the reconstruction.</t>
+        </is>
+      </c>
       <c r="M243" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -15382,6 +15418,11 @@
       </c>
       <c r="I310" s="41" t="n"/>
       <c r="J310" s="41" t="n"/>
+      <c r="K310" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). CHECKED, NO CHANGE NEEDED. Ledger #112 corrected the ATTRIBUTION of P12's coherence term, not the formula: 'The formula stands; the attribution does not.' Sigma = Coh - Str - Grad is unchanged. What moved is that the build-verified/MEASURED label belongs to Grad, which is rows 191 and 199, not here.</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="15.75" customHeight="1" s="39">
       <c r="A311" s="41" t="inlineStr">
@@ -16546,28 +16587,37 @@
       </c>
       <c r="C340" s="41" t="inlineStr">
         <is>
-          <t>xi_canonical = 1.7575 lu (cross-scale operating point); the 0.6 three-regime-RG transition exponent</t>
+          <t>xi_canonical ~ 1.8 +/- 0.3 lu (cross-scale operating point), MEASURED on the certified substrate</t>
         </is>
       </c>
       <c r="D340" s="41" t="inlineStr">
         <is>
-          <t>Selected/Inherited</t>
+          <t>Measured</t>
         </is>
       </c>
       <c r="E340" s="41" t="n"/>
-      <c r="F340" s="41" t="n"/>
+      <c r="F340" s="41" t="inlineStr">
+        <is>
+          <t>10 seeds x 40 snapshots (400 total), 64^2 periodic, via the simulator of record r2_grf_falsifier_tests.py; GR-SC 1.7 half-decay of the 2D radial autocorrelation</t>
+        </is>
+      </c>
       <c r="G340" s="41" t="inlineStr">
         <is>
-          <t>Canon-INTERNAL (NOT derived from primitives) — a benchmark, NOT a solved prediction ('the 0.6 problem' is not a solution); sourced to memory files (Staleness #4)</t>
+          <t>artefact mean 1.7575 with std 0.3035 - a 17% spread, per-seed range 1.623-2.191; canon-INTERNAL (not derived from primitives)</t>
         </is>
       </c>
       <c r="H340" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>CORRECTED 2026-09-06 - was Selected/Inherited, value quoted as 1.7575, and sourced to memory files</t>
         </is>
       </c>
       <c r="I340" s="41" t="n"/>
       <c r="J340" s="41" t="n"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). OVERTAKEN THREE TIMES OVER by 2026-09-05 work, none of which reached this row. (1) gravity #47: xi_canonical is MEASURED, not memory-floating - Paper_096 audit row 7 was re-tiered I -&gt; Measured, and the artefact is named (ed-lab/outputs/ed_sc_3_1/xi_canonical.json). So 'sourced to memory files (Staleness #4)' was wrong, and foundations staleness #4 is resolved. (2) Same item: the PRECISION is a four-significant-figure overstatement - 1.7575 against a std of 0.3035, five significant figures on a number uncertain in its first decimal place. The honest value is ~1.8 +/- 0.3. (3) gravity #50: the 0.6 exponent is NOT the same object as this one, so it has been split off this row; gravity #48 records it as REDUCED, not derived, and #50 that Paper_097's exponent is unsourced. NOTE the two arcs quote the rounding differently - gravity #47 says ~1.8 +/- 0.3, soft-matter #2 says 1.76 +/- 0.30, both from the same artefact. Worth making agree.</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="39">
       <c r="A341" s="41" t="inlineStr">
@@ -16653,7 +16703,7 @@
         </is>
       </c>
       <c r="J342" s="41" t="n"/>
-      <c r="K342" t="inlineStr">
+      <c r="K342" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#125). STALE WORDING CORRECTED 2026-09-06: this cell read 'form-derived, ~10% parameter-free match'. Same partial propagation as row 45.</t>
         </is>
@@ -19230,7 +19280,48 @@
         </is>
       </c>
     </row>
-    <row r="407" ht="15.75" customHeight="1" s="39"/>
+    <row r="407" ht="15.75" customHeight="1" s="39">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>097</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>The 0.6 three-regime-RG transition exponent</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Selected/Inherited</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>REDUCED, not derived (gravity #48); Paper_097's exponent is UNSOURCED (gravity #50)</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>current - split off row 340 on 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#126). NEW ROW, splitting the 0.6 off row 340. gravity #50 (2026-09-05) settled that the two numbers are NOT the same object, and #48 that 0.6 is REDUCED rather than derived with its tier unchanged. Appended, not inserted, so no existing row number moves.</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
     <row r="408" ht="15.75" customHeight="1" s="39"/>
     <row r="409" ht="15.75" customHeight="1" s="39"/>
     <row r="410" ht="15.75" customHeight="1" s="39"/>
@@ -24458,7 +24549,7 @@
         </is>
       </c>
       <c r="E7" s="41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -24734,7 +24825,7 @@
         </is>
       </c>
       <c r="E19" s="41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -24757,7 +24848,7 @@
         </is>
       </c>
       <c r="E20" s="41" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="39"/>
@@ -25788,7 +25879,7 @@
         </is>
       </c>
       <c r="B3" s="33" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -25865,6 +25956,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
@@ -25942,6 +26034,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
@@ -25983,6 +26076,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -26097,6 +26191,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
@@ -26153,6 +26248,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
@@ -26268,6 +26364,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -1524,7 +1524,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
@@ -2116,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M407"/>
+  <dimension ref="A1:M436"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="39" min="1" max="1"/>
@@ -7146,7 +7145,7 @@
         </is>
       </c>
       <c r="J112" s="41" t="n"/>
-      <c r="K112" t="inlineStr">
+      <c r="K112" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#126). CHECKED, CLEAN. gravity #29 (2026-09-04) fixed a cross-arc tier disagreement on c_T = c (D-structural in gravity, Inherited in dynamics). This row already reads 'speed=c ... all INHERITED', which is the side the fix landed on. No change.</t>
         </is>
@@ -7454,7 +7453,7 @@
         </is>
       </c>
       <c r="J119" s="41" t="n"/>
-      <c r="K119" t="inlineStr">
+      <c r="K119" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#126). CHECKED, CLEAN. gravity #24 (2026-09-04) audited Paper_038_5 and found 'the paper is honest, the README is not'; the force-vs-stipulate residual was confirmed and makes the MEMORY pointer stale, not section 3.5. This row already carries that residual in its own Inherited/Open cell. No change.</t>
         </is>
@@ -7508,7 +7507,7 @@
         </is>
       </c>
       <c r="J120" s="41" t="n"/>
-      <c r="K120" t="inlineStr">
+      <c r="K120" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#126). FLAGGED, NOT RE-TIERED - this needs the author, not me. gravity #19 (2026-09-04) found that Paper_KM-I and Paper_030 handle the HIGH-acceleration limit by two different and incompatible mechanisms, and neither cites the other's: Paper_030 section 7.1 uses a SWITCH (three regimes, P14 inactive above a0), while KM-I uses a smooth Cassini-constrained family - which is what this row's own Inherited/Open cell records. #19 is explicit that THE FINDING IS NOT IN KM-I: KM-I is careful, labels its hinge D conditional on I-030, and says outright that it carries Paper_030's law rather than re-deriving it. But #19 also says an earlier item 'named the wrong one as standing', and #34 (2026-09-04) subsequently DERIVED the switch. This row's Status still reads 'THE STANDING MOND RESULT' with no record of that tension. The claim itself is not disputed and KM-I is not falsified.</t>
         </is>
@@ -16613,7 +16612,7 @@
       </c>
       <c r="I340" s="41" t="n"/>
       <c r="J340" s="41" t="n"/>
-      <c r="K340" t="inlineStr">
+      <c r="K340" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#126). OVERTAKEN THREE TIMES OVER by 2026-09-05 work, none of which reached this row. (1) gravity #47: xi_canonical is MEASURED, not memory-floating - Paper_096 audit row 7 was re-tiered I -&gt; Measured, and the artefact is named (ed-lab/outputs/ed_sc_3_1/xi_canonical.json). So 'sourced to memory files (Staleness #4)' was wrong, and foundations staleness #4 is resolved. (2) Same item: the PRECISION is a four-significant-figure overstatement - 1.7575 against a std of 0.3035, five significant figures on a number uncertain in its first decimal place. The honest value is ~1.8 +/- 0.3. (3) gravity #50: the 0.6 exponent is NOT the same object as this one, so it has been split off this row; gravity #48 records it as REDUCED, not derived, and #50 that Paper_097's exponent is unsourced. NOTE the two arcs quote the rounding differently - gravity #47 says ~1.8 +/- 0.3, soft-matter #2 says 1.76 +/- 0.30, both from the same artefact. Worth making agree.</t>
         </is>
@@ -19281,76 +19280,1410 @@
       </c>
     </row>
     <row r="407" ht="15.75" customHeight="1" s="39">
-      <c r="A407" t="inlineStr">
+      <c r="A407" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B407" s="0" t="inlineStr">
         <is>
           <t>097</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
+      <c r="C407" s="0" t="inlineStr">
         <is>
           <t>The 0.6 three-regime-RG transition exponent</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
+      <c r="D407" s="0" t="inlineStr">
         <is>
           <t>Selected/Inherited</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
+      <c r="G407" s="0" t="inlineStr">
         <is>
           <t>REDUCED, not derived (gravity #48); Paper_097's exponent is UNSOURCED (gravity #50)</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
+      <c r="H407" s="0" t="inlineStr">
         <is>
           <t>current - split off row 340 on 2026-09-06</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr">
+      <c r="K407" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#126). NEW ROW, splitting the 0.6 off row 340. gravity #50 (2026-09-05) settled that the two numbers are NOT the same object, and #48 that 0.6 is REDUCED rather than derived with its tier unchanged. Appended, not inserted, so no existing row number moves.</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr">
+      <c r="M407" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
-    <row r="408" ht="15.75" customHeight="1" s="39"/>
-    <row r="409" ht="15.75" customHeight="1" s="39"/>
-    <row r="410" ht="15.75" customHeight="1" s="39"/>
-    <row r="411" ht="15.75" customHeight="1" s="39"/>
-    <row r="412" ht="15.75" customHeight="1" s="39"/>
-    <row r="413" ht="15.75" customHeight="1" s="39"/>
-    <row r="414" ht="15.75" customHeight="1" s="39"/>
-    <row r="415" ht="15.75" customHeight="1" s="39"/>
-    <row r="416" ht="15.75" customHeight="1" s="39"/>
-    <row r="417" ht="15.75" customHeight="1" s="39"/>
-    <row r="418" ht="15.75" customHeight="1" s="39"/>
-    <row r="419" ht="15.75" customHeight="1" s="39"/>
-    <row r="420" ht="15.75" customHeight="1" s="39"/>
-    <row r="421" ht="15.75" customHeight="1" s="39"/>
-    <row r="422" ht="15.75" customHeight="1" s="39"/>
-    <row r="423" ht="15.75" customHeight="1" s="39"/>
-    <row r="424" ht="15.75" customHeight="1" s="39"/>
-    <row r="425" ht="15.75" customHeight="1" s="39"/>
-    <row r="426" ht="15.75" customHeight="1" s="39"/>
-    <row r="427" ht="15.75" customHeight="1" s="39"/>
-    <row r="428" ht="15.75" customHeight="1" s="39"/>
-    <row r="429" ht="15.75" customHeight="1" s="39"/>
-    <row r="430" ht="15.75" customHeight="1" s="39"/>
-    <row r="431" ht="15.75" customHeight="1" s="39"/>
-    <row r="432" ht="15.75" customHeight="1" s="39"/>
-    <row r="433" ht="15.75" customHeight="1" s="39"/>
-    <row r="434" ht="15.75" customHeight="1" s="39"/>
-    <row r="435" ht="15.75" customHeight="1" s="39"/>
-    <row r="436" ht="15.75" customHeight="1" s="39"/>
+    <row r="408" ht="15.75" customHeight="1" s="39">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Paper_004_GleasonUniqueness</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>P-Gleason-Compatibility - Compatibility of the substrate bandwidth assignment with Gleason's frame-function requirement. Now PARTIALLY DERIVED in a bookkeeping sense: the current P04 defines bandwidth as a bare function of (K,u).</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>declared in 6 papers (foundations, qm-kinematics, substrate-evaluation)</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 6 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="15.75" customHeight="1" s="39">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Paper_ED_SC_4_1_BH_CosmicDecoupling</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>P-S1-Invariant - Substrate-level S1 kernel-content is preserved across canonical-operating-point scale transformations (Paper_096).</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>declared in 6 papers (cosmology, foundations)</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 6 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="15.75" customHeight="1" s="39">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Paper_015_T17_GaugeFields</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>P-Bundle-Definition - A substrate rule-type bundle is defined as the substrate-level structure with base = substrate locus index, fiber = channel set with $U(1)$ polarity, connection = polarity-transport, structure group = $U(1)$, rule-type label = $\tau_\bullet$. Substrate-level definition.</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>declared in 5 papers (foundations, qft)</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="15.75" customHeight="1" s="39">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Paper_ED_SC_4_1_BH_CosmicDecoupling</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>P-Cascade-Continuity - Coarse-graining between scale regimes is continuous under DCGT (Paper_091).</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>declared in 5 papers (cosmology, foundations)</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="15.75" customHeight="1" s="39">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Paper_087_13Primitives</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>P-Commitment-Advancement - A commitment event that selects a PROPAGATION-CARRYING channel advances the chain's locus; one that selects a NON-PROPAGATING channel does not. The channel-to-locus bridge. ADOPTED 2026-09-06 on AP's decision (gravity ledger #117); P11 selects a channel and is silent on the locus, and both the propagation and Higgs/dwell arcs needed opposite ends of this.</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>declared in 5 papers (foundations, substrate-evaluation)</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="15.75" customHeight="1" s="39">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Paper_087_13Primitives</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>P-Connection-Naming - Polarity-transport plays the CONNECTION role in the substrate fiber-bundle analog (Paper_015 sec 2). Substrate-ontological naming.</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>declared in 5 papers (foundations, qft)</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="15.75" customHeight="1" s="39">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Paper_015_T17_GaugeFields</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>P-Fiber-Naming - The channel set at substrate locus $u$ plays the fiber role in the substrate fiber-bundle analog. This is a substrate-ontological naming, not derived from P07. P07 fixes channels as ontological primitives; the fiber-role identification is a definitional commitment.</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>declared in 5 papers (foundations, qft)</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="15.75" customHeight="1" s="39">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Paper_087_13Primitives</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>P-StructureGroup-Naming - U(1) as the substrate STRUCTURE GROUP (Paper_015 sec 2). Substrate-ontological naming.</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>declared in 5 papers (foundations, qft)</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="15.75" customHeight="1" s="39">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Paper_KM-I_KhrononMOND</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>P-Bilocal-Count - N_bilocal = N_horizon = N(R). Named 2026-09-04 (gravity Staleness #16), closing the dropped channel-count factors in the bilocal geometric mean.</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>declared in 4 papers (foundations, gravity)</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 4 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="15.75" customHeight="1" s="39">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Paper_024_LindbladLimit</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>P-Factorized-IC - Initial system-environment substrate state factorizes: $\rho_{\mathrm{tot}}(0) = \rho_{\mathrm{sys}}(0) \otimes \rho_{\mathrm{env}}(0)$.</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>declared in 4 papers (foundations, predictions, qft)</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 4 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="15.75" customHeight="1" s="39">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Paper_UnifiedP04TransportBudget</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>P-Band-Partition - The four channel classes are DISJOINT and EXHAUSTIVE over K(u). Named 2026-09-05 (Branch 3): the bands are a classification of the channel index set summed by P04, NOT a decomposition of b_K. Disjointness is the clause that bites - a channel can both transport polarity (P05) and be phase-randomized at commitment (P11); what separates them is individuation, so the postulate is discharged RELATIVE TO a choice of system S and the bands are relational, not intrinsic.</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>declared in 3 papers (foundations, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="15.75" customHeight="1" s="39">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Paper_080_NS_Q_Factor</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>P-Canonical-Operating-Point-NS-Q - The substrate-level "canonical operating point" is defined by simultaneous saturation of P04 bandwidth-additivity + P07 channel structure + V5 finite-memory at characteristic values $\xi_{\mathrm{canonical}}$.</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>declared in 3 papers (cosmology, q-compute, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="15.75" customHeight="1" s="39">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Soft-matter</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Paper_077_NS_Smoothness_R1</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>P-Obstruction-Sufficient - The vortex-stretching obstruction (Paper_084) is structurally sufficient to prevent BKM integral divergence under R1 dissipation.</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>declared in 3 papers (soft-matter, substrate-evaluation)</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="15.75" customHeight="1" s="39">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Paper_012_RB1_RateOfBecoming</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>P-Substrate-c-Constancy - Substrate $c$ is invariant under any admissible coarse-graining variation.</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>declared in 3 papers (gravity, qm-kinematics)</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="15.75" customHeight="1" s="39">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Paper_033_AcousticMetric</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>P-AcousticMetric - (Substrate-graph acoustic metric): Substrate-graph kinematic-flow content + cumulative-strain content produces a substrate-level acoustic metric $g^{\alpha\beta}$ that DCGT-coarse-grains to a continuum Lorentzian metric (signature $(-+++)$). Substrate-level identification commitment for emergent-met</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (gravity)</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="15.75" customHeight="1" s="39">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Paper_096_CrossScaleInvariance</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>P-Canonical-Operating-Point-ED-SC - The canonical operating point xi_canonical ~ 1.8 +/- 0.3 lu. NOTE the postulate itself already flags that this is 'quoted elsewhere as 1.7575' - which is exactly the unsupported precision corrected on sheet row 340 on 2026-09-06. The corpus had written the correction into a postulate before the sheet caught up.</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, q-compute)</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="15.75" customHeight="1" s="39">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Paper_078_NS_Turb_P7_Cascade</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>P-Channel-Hierarchy - P07 channel structure supports a scale-indexed hierarchy of substrate channels; energy transfer between channels is the substrate-level analog of cascade.</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="15.75" customHeight="1" s="39">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Paper_027_Newtons_G</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>P-G-Closure - (coefficient closure on the $G$ assembly). The dimensionless coefficient in the substrate assembly of $G$ from $c$, $\hbar$ and $\ell_{\mathrm{ED}}$ is unity</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, gravity)</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="15.75" customHeight="1" s="39">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Paper_UnifiedP04TransportBudget</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>P-Locus-Bandwidth-Bound - A finite per-locus bandwidth budget. Canonical P04 gives NON-NEGATIVITY, not an upper bound, so any arc needing a finite per-locus budget must name one (soft-matter/Paper_UnifiedP04TransportBudget sec 5). Compare entanglement/Paper_065_Monogamy, which does this correctly via P-V5-Budget + I-V5.</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="15.75" customHeight="1" s="39">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Paper_085_UniversalMobilityLaw</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>P-Mobility-Maxwell-Correction - At finite frequency, the effective mobility acquires a Maxwell-viscoelastic correction from V5 finite memory.</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="15.75" customHeight="1" s="39">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Paper_ED_SC_4_5_SoftMatter_SCBU</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>P-Mobility-V1-Friction - Friction zeta ~ m/tau_V1, with finite-frequency Maxwell viscoelasticity via P-Mobility-Maxwell-Correction (Paper_085).</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="15.75" customHeight="1" s="39">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Paper_020_YM3_OSPositivity</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>P-OS-Reflection-Symmetry - The substrate is invariant under Euclidean-time reflection. Codifies the symmetry underlying $\Theta$'s action.</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (qft)</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="15.75" customHeight="1" s="39">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Soft-matter</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Paper_079_P4_NN_Rheology</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>P-Packing-Budget-Saturation - As packing fraction $\phi$ approaches a substrate-level maximum $\phi_{\max}$, the P04 bandwidth budget per substrate cell saturates; effective viscosity diverges in the form $\eta(\phi) = \eta_0 (1 - \phi/\phi_{\max})^{-n}$ for some exponent $n$.</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (soft-matter)</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="15.75" customHeight="1" s="39">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Paper_080_NS_Q_Factor</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>P-Q-Factor-Form - The Q-factor at the canonical operating point is a ratio of substrate-level stored energy budget (P04) to per-cycle dissipation (V5-controlled relaxation).</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="15.75" customHeight="1" s="39">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Soft-matter</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Paper_077_NS_Smoothness_R1</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>P-R1-Sufficient-Strength - The R1 substrate-derived kinematic viscosity $\nu \sim \ell_{V1}^2/\tau_{V1}$ (Paper_076) is sufficient to bound enstrophy growth at the substrate level for finite time intervals.</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (soft-matter, substrate-evaluation)</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="15.75" customHeight="1" s="39">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Paper_016_MinimalCoupling</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>P-Substrate-Covariant-Derivative-Construction - (substrate-level finite-difference covariant-derivative construction matching standard form) + P-Polarity-Connection-Match (substrate-level polarity-transport coarse-grains to continuum gauge connection).</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (qft)</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="15.75" customHeight="1" s="39">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Paper_097_RG_0p6_Problem</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>P-Three-Regime-RG - The Wilsonian-RG flow of substrate effective kernels exhibits three distinct regimes (UV, transition, IR) separated by the V1 and V5 scales.</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, predictions)</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="15.75" customHeight="1" s="39">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Paper_013_V1_VacuumKernel</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>P-V1-FormFactor - The momentum-space V1 form factor $\hat{K}_{V1}(p)$ decays for $|p|\ell_{V1} \gtrsim 1$ (UV regularization).</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (qft, relativistic-qm)</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="15.75" customHeight="1" s="39">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Paper_ED_SC_4_5_SoftMatter_SCBU</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>P-V5-Maxwell-Identification - V5 finite memory tau_V5 produces Maxwell-form stress relaxation; tau_M ~ tau_V5 (Paper_074, Paper_079).</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
     <row r="437" ht="15.75" customHeight="1" s="39"/>
     <row r="438" ht="15.75" customHeight="1" s="39"/>
     <row r="439" ht="15.75" customHeight="1" s="39"/>
@@ -24687,7 +26020,7 @@
         </is>
       </c>
       <c r="E13" s="41" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -25919,7 +27252,7 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -25956,7 +27289,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
@@ -26034,7 +27366,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
@@ -26328,11 +27659,11 @@
         </is>
       </c>
       <c r="B21" s="0" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>+13 = 28. THIS workbook's basis - the 'live' flag in the Postulate column</t>
+          <t>+13 = 31. THIS workbook's basis - the 'live' flag in the Postulate column. Rose from 15 on 2026-09-06 when C1 added the postulates named this week (P-Band-Partition, P-Locus-Bandwidth-Bound, P-Commitment-Advancement). The other 26 C1 additions are marked 'live status NOT assessed' and are deliberately NOT counted here.</t>
         </is>
       </c>
     </row>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C340" s="41" t="inlineStr">
         <is>
-          <t>xi_canonical ~ 1.8 +/- 0.3 lu (cross-scale operating point), MEASURED on the certified substrate</t>
+          <t>xi_canonical = 1.740 +/- 0.028 lu (cross-scale operating point), MEASURED on the certified substrate</t>
         </is>
       </c>
       <c r="D340" s="41" t="inlineStr">
@@ -16602,19 +16602,19 @@
       </c>
       <c r="G340" s="41" t="inlineStr">
         <is>
-          <t>artefact mean 1.7575 with std 0.3035 - a 17% spread, per-seed range 1.623-2.191; canon-INTERNAL (not derived from primitives)</t>
+          <t>40 seeds x 40 snapshots; per-snapshot spread 0.334, per-seed 0.179, standard error 0.028; canon-INTERNAL (not derived from primitives)</t>
         </is>
       </c>
       <c r="H340" s="41" t="inlineStr">
         <is>
-          <t>CORRECTED 2026-09-06 - was Selected/Inherited, value quoted as 1.7575, and sourced to memory files</t>
+          <t>TIGHTENED 2026-09-06 - was 1.7575, then 1.8 +/- 0.3</t>
         </is>
       </c>
       <c r="I340" s="41" t="n"/>
       <c r="J340" s="41" t="n"/>
       <c r="K340" s="0" t="inlineStr">
         <is>
-          <t>VERIFIED 2026-09-06 (#126). OVERTAKEN THREE TIMES OVER by 2026-09-05 work, none of which reached this row. (1) gravity #47: xi_canonical is MEASURED, not memory-floating - Paper_096 audit row 7 was re-tiered I -&gt; Measured, and the artefact is named (ed-lab/outputs/ed_sc_3_1/xi_canonical.json). So 'sourced to memory files (Staleness #4)' was wrong, and foundations staleness #4 is resolved. (2) Same item: the PRECISION is a four-significant-figure overstatement - 1.7575 against a std of 0.3035, five significant figures on a number uncertain in its first decimal place. The honest value is ~1.8 +/- 0.3. (3) gravity #50: the 0.6 exponent is NOT the same object as this one, so it has been split off this row; gravity #48 records it as REDUCED, not derived, and #50 that Paper_097's exponent is unsourced. NOTE the two arcs quote the rounding differently - gravity #47 says ~1.8 +/- 0.3, soft-matter #2 says 1.76 +/- 0.30, both from the same artefact. Worth making agree.</t>
+          <t>VERIFIED 2026-09-06 (#130). TIGHTENED 2026-09-06: xi = 1.740 +/- 0.028 lu (40 seeds, 1600 snapshots, same estimator imported so the method cannot drift). The +/- 0.30 previously here is the per-SNAPSHOT spread, not the uncertainty on the mean: per-snapshot 0.334, per-seed 0.179, standard error 0.028. So the corpus first OVERSTATED the precision (1.7575, five significant figures) and then UNDERSTATED it (1.8 +/- 0.3); the supported figure is three significant figures, 1.74. Caveat: 4 of 40 individual seeds exceed 2.0.  [earlier: VERIFIED 2026-09-06 (#126). OVERTAKEN THREE TIMES OVER by 2026-09-05 work, none of which reached this row. (1) gravity #47: xi_canonical is MEASURED, not memory-floating - Paper_096 audit row 7 was re-tiered I -&gt; Measured, and the artefact is named (ed-lab/outputs/ed_sc_3_1/xi_canonical.json). So 'sourced to memory files (Staleness #4)' was wrong, and foundations staleness #4 is resolved. (2) Same]</t>
         </is>
       </c>
     </row>
@@ -19322,1363 +19322,1363 @@
       </c>
     </row>
     <row r="408" ht="15.75" customHeight="1" s="39">
-      <c r="A408" t="inlineStr">
+      <c r="A408" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B408" s="0" t="inlineStr">
         <is>
           <t>Paper_004_GleasonUniqueness</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C408" s="0" t="inlineStr">
         <is>
           <t>P-Gleason-Compatibility - Compatibility of the substrate bandwidth assignment with Gleason's frame-function requirement. Now PARTIALLY DERIVED in a bookkeeping sense: the current P04 defines bandwidth as a bare function of (K,u).</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr">
+      <c r="D408" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr">
+      <c r="G408" s="0" t="inlineStr">
         <is>
           <t>declared in 6 papers (foundations, qm-kinematics, substrate-evaluation)</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
+      <c r="H408" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J408" t="inlineStr">
+      <c r="J408" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr">
+      <c r="K408" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 6 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr">
+      <c r="M408" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="409" ht="15.75" customHeight="1" s="39">
-      <c r="A409" t="inlineStr">
+      <c r="A409" s="0" t="inlineStr">
         <is>
           <t>Cosmology</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B409" s="0" t="inlineStr">
         <is>
           <t>Paper_ED_SC_4_1_BH_CosmicDecoupling</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C409" s="0" t="inlineStr">
         <is>
           <t>P-S1-Invariant - Substrate-level S1 kernel-content is preserved across canonical-operating-point scale transformations (Paper_096).</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
+      <c r="D409" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr">
+      <c r="G409" s="0" t="inlineStr">
         <is>
           <t>declared in 6 papers (cosmology, foundations)</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
+      <c r="H409" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J409" t="inlineStr">
+      <c r="J409" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr">
+      <c r="K409" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 6 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M409" t="inlineStr">
+      <c r="M409" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="410" ht="15.75" customHeight="1" s="39">
-      <c r="A410" t="inlineStr">
+      <c r="A410" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
+      <c r="B410" s="0" t="inlineStr">
         <is>
           <t>Paper_015_T17_GaugeFields</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
+      <c r="C410" s="0" t="inlineStr">
         <is>
           <t>P-Bundle-Definition - A substrate rule-type bundle is defined as the substrate-level structure with base = substrate locus index, fiber = channel set with $U(1)$ polarity, connection = polarity-transport, structure group = $U(1)$, rule-type label = $\tau_\bullet$. Substrate-level definition.</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
+      <c r="D410" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr">
+      <c r="G410" s="0" t="inlineStr">
         <is>
           <t>declared in 5 papers (foundations, qft)</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
+      <c r="H410" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr">
+      <c r="J410" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr">
+      <c r="K410" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr">
+      <c r="M410" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="411" ht="15.75" customHeight="1" s="39">
-      <c r="A411" t="inlineStr">
+      <c r="A411" s="0" t="inlineStr">
         <is>
           <t>Cosmology</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B411" s="0" t="inlineStr">
         <is>
           <t>Paper_ED_SC_4_1_BH_CosmicDecoupling</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr">
+      <c r="C411" s="0" t="inlineStr">
         <is>
           <t>P-Cascade-Continuity - Coarse-graining between scale regimes is continuous under DCGT (Paper_091).</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr">
+      <c r="D411" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr">
+      <c r="G411" s="0" t="inlineStr">
         <is>
           <t>declared in 5 papers (cosmology, foundations)</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
+      <c r="H411" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J411" t="inlineStr">
+      <c r="J411" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr">
+      <c r="K411" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M411" t="inlineStr">
+      <c r="M411" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="412" ht="15.75" customHeight="1" s="39">
-      <c r="A412" t="inlineStr">
+      <c r="A412" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B412" s="0" t="inlineStr">
         <is>
           <t>Paper_087_13Primitives</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
+      <c r="C412" s="0" t="inlineStr">
         <is>
           <t>P-Commitment-Advancement - A commitment event that selects a PROPAGATION-CARRYING channel advances the chain's locus; one that selects a NON-PROPAGATING channel does not. The channel-to-locus bridge. ADOPTED 2026-09-06 on AP's decision (gravity ledger #117); P11 selects a channel and is silent on the locus, and both the propagation and Higgs/dwell arcs needed opposite ends of this.</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
+      <c r="D412" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
+      <c r="G412" s="0" t="inlineStr">
         <is>
           <t>declared in 5 papers (foundations, substrate-evaluation)</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
+      <c r="H412" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr">
+      <c r="J412" s="0" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr">
+      <c r="K412" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr">
+      <c r="M412" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="413" ht="15.75" customHeight="1" s="39">
-      <c r="A413" t="inlineStr">
+      <c r="A413" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B413" s="0" t="inlineStr">
         <is>
           <t>Paper_087_13Primitives</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
+      <c r="C413" s="0" t="inlineStr">
         <is>
           <t>P-Connection-Naming - Polarity-transport plays the CONNECTION role in the substrate fiber-bundle analog (Paper_015 sec 2). Substrate-ontological naming.</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
+      <c r="D413" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr">
+      <c r="G413" s="0" t="inlineStr">
         <is>
           <t>declared in 5 papers (foundations, qft)</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
+      <c r="H413" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J413" t="inlineStr">
+      <c r="J413" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr">
+      <c r="K413" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr">
+      <c r="M413" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="414" ht="15.75" customHeight="1" s="39">
-      <c r="A414" t="inlineStr">
+      <c r="A414" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B414" s="0" t="inlineStr">
         <is>
           <t>Paper_015_T17_GaugeFields</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C414" s="0" t="inlineStr">
         <is>
           <t>P-Fiber-Naming - The channel set at substrate locus $u$ plays the fiber role in the substrate fiber-bundle analog. This is a substrate-ontological naming, not derived from P07. P07 fixes channels as ontological primitives; the fiber-role identification is a definitional commitment.</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
+      <c r="D414" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr">
+      <c r="G414" s="0" t="inlineStr">
         <is>
           <t>declared in 5 papers (foundations, qft)</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
+      <c r="H414" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J414" t="inlineStr">
+      <c r="J414" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr">
+      <c r="K414" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr">
+      <c r="M414" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="415" ht="15.75" customHeight="1" s="39">
-      <c r="A415" t="inlineStr">
+      <c r="A415" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B415" s="0" t="inlineStr">
         <is>
           <t>Paper_087_13Primitives</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C415" s="0" t="inlineStr">
         <is>
           <t>P-StructureGroup-Naming - U(1) as the substrate STRUCTURE GROUP (Paper_015 sec 2). Substrate-ontological naming.</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
+      <c r="D415" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr">
+      <c r="G415" s="0" t="inlineStr">
         <is>
           <t>declared in 5 papers (foundations, qft)</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
+      <c r="H415" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J415" t="inlineStr">
+      <c r="J415" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr">
+      <c r="K415" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 5 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr">
+      <c r="M415" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="416" ht="15.75" customHeight="1" s="39">
-      <c r="A416" t="inlineStr">
+      <c r="A416" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B416" s="0" t="inlineStr">
         <is>
           <t>Paper_KM-I_KhrononMOND</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr">
+      <c r="C416" s="0" t="inlineStr">
         <is>
           <t>P-Bilocal-Count - N_bilocal = N_horizon = N(R). Named 2026-09-04 (gravity Staleness #16), closing the dropped channel-count factors in the bilocal geometric mean.</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
+      <c r="D416" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr">
+      <c r="G416" s="0" t="inlineStr">
         <is>
           <t>declared in 4 papers (foundations, gravity)</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
+      <c r="H416" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J416" t="inlineStr">
+      <c r="J416" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr">
+      <c r="K416" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 4 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M416" t="inlineStr">
+      <c r="M416" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="417" ht="15.75" customHeight="1" s="39">
-      <c r="A417" t="inlineStr">
+      <c r="A417" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B417" s="0" t="inlineStr">
         <is>
           <t>Paper_024_LindbladLimit</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr">
+      <c r="C417" s="0" t="inlineStr">
         <is>
           <t>P-Factorized-IC - Initial system-environment substrate state factorizes: $\rho_{\mathrm{tot}}(0) = \rho_{\mathrm{sys}}(0) \otimes \rho_{\mathrm{env}}(0)$.</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr">
+      <c r="D417" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr">
+      <c r="G417" s="0" t="inlineStr">
         <is>
           <t>declared in 4 papers (foundations, predictions, qft)</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
+      <c r="H417" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J417" t="inlineStr">
+      <c r="J417" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr">
+      <c r="K417" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 4 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M417" t="inlineStr">
+      <c r="M417" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="418" ht="15.75" customHeight="1" s="39">
-      <c r="A418" t="inlineStr">
+      <c r="A418" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B418" s="0" t="inlineStr">
         <is>
           <t>Paper_UnifiedP04TransportBudget</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C418" s="0" t="inlineStr">
         <is>
           <t>P-Band-Partition - The four channel classes are DISJOINT and EXHAUSTIVE over K(u). Named 2026-09-05 (Branch 3): the bands are a classification of the channel index set summed by P04, NOT a decomposition of b_K. Disjointness is the clause that bites - a channel can both transport polarity (P05) and be phase-randomized at commitment (P11); what separates them is individuation, so the postulate is discharged RELATIVE TO a choice of system S and the bands are relational, not intrinsic.</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D418" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr">
+      <c r="G418" s="0" t="inlineStr">
         <is>
           <t>declared in 3 papers (foundations, soft-matter)</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
+      <c r="H418" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J418" t="inlineStr">
+      <c r="J418" s="0" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr">
+      <c r="K418" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M418" t="inlineStr">
+      <c r="M418" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="419" ht="15.75" customHeight="1" s="39">
-      <c r="A419" t="inlineStr">
+      <c r="A419" s="0" t="inlineStr">
         <is>
           <t>Cosmology</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B419" s="0" t="inlineStr">
         <is>
           <t>Paper_080_NS_Q_Factor</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr">
+      <c r="C419" s="0" t="inlineStr">
         <is>
           <t>P-Canonical-Operating-Point-NS-Q - The substrate-level "canonical operating point" is defined by simultaneous saturation of P04 bandwidth-additivity + P07 channel structure + V5 finite-memory at characteristic values $\xi_{\mathrm{canonical}}$.</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
+      <c r="D419" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr">
+      <c r="G419" s="0" t="inlineStr">
         <is>
           <t>declared in 3 papers (cosmology, q-compute, soft-matter)</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
+      <c r="H419" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J419" t="inlineStr">
+      <c r="J419" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr">
+      <c r="K419" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M419" t="inlineStr">
+      <c r="M419" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="420" ht="15.75" customHeight="1" s="39">
-      <c r="A420" t="inlineStr">
+      <c r="A420" s="0" t="inlineStr">
         <is>
           <t>Soft-matter</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B420" s="0" t="inlineStr">
         <is>
           <t>Paper_077_NS_Smoothness_R1</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
+      <c r="C420" s="0" t="inlineStr">
         <is>
           <t>P-Obstruction-Sufficient - The vortex-stretching obstruction (Paper_084) is structurally sufficient to prevent BKM integral divergence under R1 dissipation.</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
+      <c r="D420" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
+      <c r="G420" s="0" t="inlineStr">
         <is>
           <t>declared in 3 papers (soft-matter, substrate-evaluation)</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
+      <c r="H420" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr">
+      <c r="J420" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr">
+      <c r="K420" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr">
+      <c r="M420" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="421" ht="15.75" customHeight="1" s="39">
-      <c r="A421" t="inlineStr">
+      <c r="A421" s="0" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B421" s="0" t="inlineStr">
         <is>
           <t>Paper_012_RB1_RateOfBecoming</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C421" s="0" t="inlineStr">
         <is>
           <t>P-Substrate-c-Constancy - Substrate $c$ is invariant under any admissible coarse-graining variation.</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D421" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
+      <c r="G421" s="0" t="inlineStr">
         <is>
           <t>declared in 3 papers (gravity, qm-kinematics)</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
+      <c r="H421" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J421" t="inlineStr">
+      <c r="J421" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr">
+      <c r="K421" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 3 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr">
+      <c r="M421" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="422" ht="15.75" customHeight="1" s="39">
-      <c r="A422" t="inlineStr">
+      <c r="A422" s="0" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B422" s="0" t="inlineStr">
         <is>
           <t>Paper_033_AcousticMetric</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
+      <c r="C422" s="0" t="inlineStr">
         <is>
           <t>P-AcousticMetric - (Substrate-graph acoustic metric): Substrate-graph kinematic-flow content + cumulative-strain content produces a substrate-level acoustic metric $g^{\alpha\beta}$ that DCGT-coarse-grains to a continuum Lorentzian metric (signature $(-+++)$). Substrate-level identification commitment for emergent-met</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
+      <c r="D422" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
+      <c r="G422" s="0" t="inlineStr">
         <is>
           <t>declared in 2 papers (gravity)</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
+      <c r="H422" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J422" t="inlineStr">
+      <c r="J422" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr">
+      <c r="K422" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M422" t="inlineStr">
+      <c r="M422" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="423" ht="15.75" customHeight="1" s="39">
-      <c r="A423" t="inlineStr">
+      <c r="A423" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B423" s="0" t="inlineStr">
         <is>
           <t>Paper_096_CrossScaleInvariance</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>P-Canonical-Operating-Point-ED-SC - The canonical operating point xi_canonical ~ 1.8 +/- 0.3 lu. NOTE the postulate itself already flags that this is 'quoted elsewhere as 1.7575' - which is exactly the unsupported precision corrected on sheet row 340 on 2026-09-06. The corpus had written the correction into a postulate before the sheet caught up.</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
+      <c r="C423" s="0" t="inlineStr">
+        <is>
+          <t>P-Canonical-Operating-Point-ED-SC - The canonical operating point xi_canonical = 1.740 +/- 0.028 lu (TIGHTENED 2026-09-06; the postulate's own text had already flagged that 1.7575 was quoted elsewhere)</t>
+        </is>
+      </c>
+      <c r="D423" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr">
+      <c r="G423" s="0" t="inlineStr">
         <is>
           <t>declared in 2 papers (foundations, q-compute)</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr">
+      <c r="H423" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J423" t="inlineStr">
+      <c r="J423" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr">
+      <c r="K423" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#130). TIGHTENED 2026-09-06: xi = 1.740 +/- 0.028 lu (40 seeds, 1600 snapshots, same estimator imported so the method cannot drift). The +/- 0.30 previously here is the per-SNAPSHOT spread, not the uncertainty on the mean: per-snapshot 0.334, per-seed 0.179, standard error 0.028. So the corpus first OVERSTATED the precision (1.7575, five significant figures) and then UNDERSTATED it (1.8 +/- 0.3); the supported figure is three significant figures, 1.74. Caveat: 4 of 40 individual seeds exceed 2.0.</t>
+        </is>
+      </c>
+      <c r="M423" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="15.75" customHeight="1" s="39">
+      <c r="A424" s="0" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B424" s="0" t="inlineStr">
+        <is>
+          <t>Paper_078_NS_Turb_P7_Cascade</t>
+        </is>
+      </c>
+      <c r="C424" s="0" t="inlineStr">
+        <is>
+          <t>P-Channel-Hierarchy - P07 channel structure supports a scale-indexed hierarchy of substrate channels; energy transfer between channels is the substrate-level analog of cascade.</t>
+        </is>
+      </c>
+      <c r="D424" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G424" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H424" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J424" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K424" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M423" t="inlineStr">
+      <c r="M424" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
-    <row r="424" ht="15.75" customHeight="1" s="39">
-      <c r="A424" t="inlineStr">
+    <row r="425" ht="15.75" customHeight="1" s="39">
+      <c r="A425" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Paper_078_NS_Turb_P7_Cascade</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>P-Channel-Hierarchy - P07 channel structure supports a scale-indexed hierarchy of substrate channels; energy transfer between channels is the substrate-level analog of cascade.</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t>Paper_027_Newtons_G</t>
+        </is>
+      </c>
+      <c r="C425" s="0" t="inlineStr">
+        <is>
+          <t>P-G-Closure - (coefficient closure on the $G$ assembly). The dimensionless coefficient in the substrate assembly of $G$ from $c$, $\hbar$ and $\ell_{\mathrm{ED}}$ is unity</t>
+        </is>
+      </c>
+      <c r="D425" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr">
+      <c r="G425" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, gravity)</t>
+        </is>
+      </c>
+      <c r="H425" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J425" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K425" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M425" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="15.75" customHeight="1" s="39">
+      <c r="A426" s="0" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t>Paper_UnifiedP04TransportBudget</t>
+        </is>
+      </c>
+      <c r="C426" s="0" t="inlineStr">
+        <is>
+          <t>P-Locus-Bandwidth-Bound - A finite per-locus bandwidth budget. Canonical P04 gives NON-NEGATIVITY, not an upper bound, so any arc needing a finite per-locus budget must name one (soft-matter/Paper_UnifiedP04TransportBudget sec 5). Compare entanglement/Paper_065_Monogamy, which does this correctly via P-V5-Budget + I-V5.</t>
+        </is>
+      </c>
+      <c r="D426" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G426" s="0" t="inlineStr">
         <is>
           <t>declared in 2 papers (foundations, soft-matter)</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
+      <c r="H426" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J424" t="inlineStr">
+      <c r="J426" s="0" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="K426" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M426" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="15.75" customHeight="1" s="39">
+      <c r="A427" s="0" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t>Paper_085_UniversalMobilityLaw</t>
+        </is>
+      </c>
+      <c r="C427" s="0" t="inlineStr">
+        <is>
+          <t>P-Mobility-Maxwell-Correction - At finite frequency, the effective mobility acquires a Maxwell-viscoelastic correction from V5 finite memory.</t>
+        </is>
+      </c>
+      <c r="D427" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G427" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H427" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J427" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr">
+      <c r="K427" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M424" t="inlineStr">
+      <c r="M427" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
-    <row r="425" ht="15.75" customHeight="1" s="39">
-      <c r="A425" t="inlineStr">
+    <row r="428" ht="15.75" customHeight="1" s="39">
+      <c r="A428" s="0" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t>Paper_ED_SC_4_5_SoftMatter_SCBU</t>
+        </is>
+      </c>
+      <c r="C428" s="0" t="inlineStr">
+        <is>
+          <t>P-Mobility-V1-Friction - Friction zeta ~ m/tau_V1, with finite-frequency Maxwell viscoelasticity via P-Mobility-Maxwell-Correction (Paper_085).</t>
+        </is>
+      </c>
+      <c r="D428" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G428" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H428" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J428" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K428" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M428" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="15.75" customHeight="1" s="39">
+      <c r="A429" s="0" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t>Paper_020_YM3_OSPositivity</t>
+        </is>
+      </c>
+      <c r="C429" s="0" t="inlineStr">
+        <is>
+          <t>P-OS-Reflection-Symmetry - The substrate is invariant under Euclidean-time reflection. Codifies the symmetry underlying $\Theta$'s action.</t>
+        </is>
+      </c>
+      <c r="D429" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G429" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (qft)</t>
+        </is>
+      </c>
+      <c r="H429" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J429" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K429" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M429" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="15.75" customHeight="1" s="39">
+      <c r="A430" s="0" t="inlineStr">
+        <is>
+          <t>Soft-matter</t>
+        </is>
+      </c>
+      <c r="B430" s="0" t="inlineStr">
+        <is>
+          <t>Paper_079_P4_NN_Rheology</t>
+        </is>
+      </c>
+      <c r="C430" s="0" t="inlineStr">
+        <is>
+          <t>P-Packing-Budget-Saturation - As packing fraction $\phi$ approaches a substrate-level maximum $\phi_{\max}$, the P04 bandwidth budget per substrate cell saturates; effective viscosity diverges in the form $\eta(\phi) = \eta_0 (1 - \phi/\phi_{\max})^{-n}$ for some exponent $n$.</t>
+        </is>
+      </c>
+      <c r="D430" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G430" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (soft-matter)</t>
+        </is>
+      </c>
+      <c r="H430" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J430" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K430" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M430" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="15.75" customHeight="1" s="39">
+      <c r="A431" s="0" t="inlineStr">
+        <is>
+          <t>Cosmology</t>
+        </is>
+      </c>
+      <c r="B431" s="0" t="inlineStr">
+        <is>
+          <t>Paper_080_NS_Q_Factor</t>
+        </is>
+      </c>
+      <c r="C431" s="0" t="inlineStr">
+        <is>
+          <t>P-Q-Factor-Form - The Q-factor at the canonical operating point is a ratio of substrate-level stored energy budget (P04) to per-cycle dissipation (V5-controlled relaxation).</t>
+        </is>
+      </c>
+      <c r="D431" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G431" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (cosmology, soft-matter)</t>
+        </is>
+      </c>
+      <c r="H431" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J431" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K431" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M431" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="15.75" customHeight="1" s="39">
+      <c r="A432" s="0" t="inlineStr">
+        <is>
+          <t>Soft-matter</t>
+        </is>
+      </c>
+      <c r="B432" s="0" t="inlineStr">
+        <is>
+          <t>Paper_077_NS_Smoothness_R1</t>
+        </is>
+      </c>
+      <c r="C432" s="0" t="inlineStr">
+        <is>
+          <t>P-R1-Sufficient-Strength - The R1 substrate-derived kinematic viscosity $\nu \sim \ell_{V1}^2/\tau_{V1}$ (Paper_076) is sufficient to bound enstrophy growth at the substrate level for finite time intervals.</t>
+        </is>
+      </c>
+      <c r="D432" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G432" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (soft-matter, substrate-evaluation)</t>
+        </is>
+      </c>
+      <c r="H432" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J432" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K432" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M432" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="15.75" customHeight="1" s="39">
+      <c r="A433" s="0" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B433" s="0" t="inlineStr">
+        <is>
+          <t>Paper_016_MinimalCoupling</t>
+        </is>
+      </c>
+      <c r="C433" s="0" t="inlineStr">
+        <is>
+          <t>P-Substrate-Covariant-Derivative-Construction - (substrate-level finite-difference covariant-derivative construction matching standard form) + P-Polarity-Connection-Match (substrate-level polarity-transport coarse-grains to continuum gauge connection).</t>
+        </is>
+      </c>
+      <c r="D433" s="0" t="inlineStr">
+        <is>
+          <t>Postulated</t>
+        </is>
+      </c>
+      <c r="G433" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (qft)</t>
+        </is>
+      </c>
+      <c r="H433" s="0" t="inlineStr">
+        <is>
+          <t>added 2026-09-06 (C1 coverage)</t>
+        </is>
+      </c>
+      <c r="J433" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K433" s="0" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
+        </is>
+      </c>
+      <c r="M433" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="15.75" customHeight="1" s="39">
+      <c r="A434" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Paper_027_Newtons_G</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>P-G-Closure - (coefficient closure on the $G$ assembly). The dimensionless coefficient in the substrate assembly of $G$ from $c$, $\hbar$ and $\ell_{\mathrm{ED}}$ is unity</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
+      <c r="B434" s="0" t="inlineStr">
+        <is>
+          <t>Paper_097_RG_0p6_Problem</t>
+        </is>
+      </c>
+      <c r="C434" s="0" t="inlineStr">
+        <is>
+          <t>P-Three-Regime-RG - The Wilsonian-RG flow of substrate effective kernels exhibits three distinct regimes (UV, transition, IR) separated by the V1 and V5 scales.</t>
+        </is>
+      </c>
+      <c r="D434" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (foundations, gravity)</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr">
+      <c r="G434" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (foundations, predictions)</t>
+        </is>
+      </c>
+      <c r="H434" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J425" t="inlineStr">
+      <c r="J434" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr">
+      <c r="K434" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M425" t="inlineStr">
+      <c r="M434" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
-    <row r="426" ht="15.75" customHeight="1" s="39">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Foundations</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Paper_UnifiedP04TransportBudget</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>P-Locus-Bandwidth-Bound - A finite per-locus bandwidth budget. Canonical P04 gives NON-NEGATIVITY, not an upper bound, so any arc needing a finite per-locus budget must name one (soft-matter/Paper_UnifiedP04TransportBudget sec 5). Compare entanglement/Paper_065_Monogamy, which does this correctly via P-V5-Budget + I-V5.</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
+    <row r="435" ht="15.75" customHeight="1" s="39">
+      <c r="A435" s="0" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B435" s="0" t="inlineStr">
+        <is>
+          <t>Paper_013_V1_VacuumKernel</t>
+        </is>
+      </c>
+      <c r="C435" s="0" t="inlineStr">
+        <is>
+          <t>P-V1-FormFactor - The momentum-space V1 form factor $\hat{K}_{V1}(p)$ decays for $|p|\ell_{V1} \gtrsim 1$ (UV regularization).</t>
+        </is>
+      </c>
+      <c r="D435" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (foundations, soft-matter)</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr">
+      <c r="G435" s="0" t="inlineStr">
+        <is>
+          <t>declared in 2 papers (qft, relativistic-qm)</t>
+        </is>
+      </c>
+      <c r="H435" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="K426" t="inlineStr">
+      <c r="J435" s="0" t="inlineStr">
+        <is>
+          <t>declared; live status NOT assessed 2026-09-06</t>
+        </is>
+      </c>
+      <c r="K435" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M426" t="inlineStr">
+      <c r="M435" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
-    <row r="427" ht="15.75" customHeight="1" s="39">
-      <c r="A427" t="inlineStr">
+    <row r="436" ht="15.75" customHeight="1" s="39">
+      <c r="A436" s="0" t="inlineStr">
         <is>
           <t>Cosmology</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Paper_085_UniversalMobilityLaw</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>P-Mobility-Maxwell-Correction - At finite frequency, the effective mobility acquires a Maxwell-viscoelastic correction from V5 finite memory.</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
+      <c r="B436" s="0" t="inlineStr">
+        <is>
+          <t>Paper_ED_SC_4_5_SoftMatter_SCBU</t>
+        </is>
+      </c>
+      <c r="C436" s="0" t="inlineStr">
+        <is>
+          <t>P-V5-Maxwell-Identification - V5 finite memory tau_V5 produces Maxwell-form stress relaxation; tau_M ~ tau_V5 (Paper_074, Paper_079).</t>
+        </is>
+      </c>
+      <c r="D436" s="0" t="inlineStr">
         <is>
           <t>Postulated</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr">
+      <c r="G436" s="0" t="inlineStr">
         <is>
           <t>declared in 2 papers (cosmology, soft-matter)</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
+      <c r="H436" s="0" t="inlineStr">
         <is>
           <t>added 2026-09-06 (C1 coverage)</t>
         </is>
       </c>
-      <c r="J427" t="inlineStr">
+      <c r="J436" s="0" t="inlineStr">
         <is>
           <t>declared; live status NOT assessed 2026-09-06</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr">
+      <c r="K436" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
         </is>
       </c>
-      <c r="M427" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="428" ht="15.75" customHeight="1" s="39">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Cosmology</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Paper_ED_SC_4_5_SoftMatter_SCBU</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>P-Mobility-V1-Friction - Friction zeta ~ m/tau_V1, with finite-frequency Maxwell viscoelasticity via P-Mobility-Maxwell-Correction (Paper_085).</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (cosmology, soft-matter)</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J428" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="429" ht="15.75" customHeight="1" s="39">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>QFT</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Paper_020_YM3_OSPositivity</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>P-OS-Reflection-Symmetry - The substrate is invariant under Euclidean-time reflection. Codifies the symmetry underlying $\Theta$'s action.</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (qft)</t>
-        </is>
-      </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J429" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="430" ht="15.75" customHeight="1" s="39">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Soft-matter</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Paper_079_P4_NN_Rheology</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>P-Packing-Budget-Saturation - As packing fraction $\phi$ approaches a substrate-level maximum $\phi_{\max}$, the P04 bandwidth budget per substrate cell saturates; effective viscosity diverges in the form $\eta(\phi) = \eta_0 (1 - \phi/\phi_{\max})^{-n}$ for some exponent $n$.</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (soft-matter)</t>
-        </is>
-      </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J430" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M430" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="431" ht="15.75" customHeight="1" s="39">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Cosmology</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Paper_080_NS_Q_Factor</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>P-Q-Factor-Form - The Q-factor at the canonical operating point is a ratio of substrate-level stored energy budget (P04) to per-cycle dissipation (V5-controlled relaxation).</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (cosmology, soft-matter)</t>
-        </is>
-      </c>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M431" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="432" ht="15.75" customHeight="1" s="39">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Soft-matter</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Paper_077_NS_Smoothness_R1</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>P-R1-Sufficient-Strength - The R1 substrate-derived kinematic viscosity $\nu \sim \ell_{V1}^2/\tau_{V1}$ (Paper_076) is sufficient to bound enstrophy growth at the substrate level for finite time intervals.</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (soft-matter, substrate-evaluation)</t>
-        </is>
-      </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K432" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M432" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="433" ht="15.75" customHeight="1" s="39">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>QFT</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Paper_016_MinimalCoupling</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>P-Substrate-Covariant-Derivative-Construction - (substrate-level finite-difference covariant-derivative construction matching standard form) + P-Polarity-Connection-Match (substrate-level polarity-transport coarse-grains to continuum gauge connection).</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (qft)</t>
-        </is>
-      </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J433" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K433" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M433" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="434" ht="15.75" customHeight="1" s="39">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>Foundations</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Paper_097_RG_0p6_Problem</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>P-Three-Regime-RG - The Wilsonian-RG flow of substrate effective kernels exhibits three distinct regimes (UV, transition, IR) separated by the V1 and V5 scales.</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (foundations, predictions)</t>
-        </is>
-      </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="435" ht="15.75" customHeight="1" s="39">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>QFT</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Paper_013_V1_VacuumKernel</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>P-V1-FormFactor - The momentum-space V1 form factor $\hat{K}_{V1}(p)$ decays for $|p|\ell_{V1} \gtrsim 1$ (UV regularization).</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (qft, relativistic-qm)</t>
-        </is>
-      </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="436" ht="15.75" customHeight="1" s="39">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>Cosmology</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Paper_ED_SC_4_5_SoftMatter_SCBU</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>P-V5-Maxwell-Identification - V5 finite memory tau_V5 produces Maxwell-form stress relaxation; tau_M ~ tau_V5 (Paper_074, Paper_079).</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>Postulated</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>declared in 2 papers (cosmology, soft-matter)</t>
-        </is>
-      </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>added 2026-09-06 (C1 coverage)</t>
-        </is>
-      </c>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>declared; live status NOT assessed 2026-09-06</t>
-        </is>
-      </c>
-      <c r="K436" t="inlineStr">
-        <is>
-          <t>VERIFIED 2026-09-06 (#127). ADDED BY C1. This is a named corpus postulate the workbook never mentioned. Included because it appears in 2 papers, so it OUTLIVES the derivation that introduced it. The 56 postulates appearing in exactly one paper are deliberately NOT added: POSTULATE_BASIS.md (research target #20) established the commitments as a breadth ladder, and a one-paper postulate is a local modelling choice like a gauge choice. Listing all 56 would bury these 29.</t>
-        </is>
-      </c>
-      <c r="M436" t="inlineStr">
+      <c r="M436" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
@@ -27188,13 +27188,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A2:B8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="43.43" customWidth="1" style="39" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -27407,7 +27406,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -27522,7 +27520,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
@@ -27579,7 +27576,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
@@ -27695,7 +27691,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M436"/>
+  <dimension ref="A1:M437"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="39" min="1" max="1"/>
@@ -20684,7 +20684,53 @@
         </is>
       </c>
     </row>
-    <row r="437" ht="15.75" customHeight="1" s="39"/>
+    <row r="437" ht="15.75" customHeight="1" s="39">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Foundations</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Universal free fall (equivalence-principle universality) under P12's literal a_C = -grad_adj Sigma_C</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>NOT established. P12 carries no inertial normalisation and the cross term scales as sqrt(b_K) in the chain's OWN bandwidth, so two chains of different bandwidth in one ambient field would accelerate differently</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>OPEN. ED HAS an inertia mechanism and it is MEASURED - a bound composite under uniform force reaches v_x = 0.72 against an unbound cluster's 0.97 (Paper_MassWithoutMass_BindingInertia) - but that paper's preamble item 4 concedes the equivalence-principle reading is 'a consistent interpretation, not an independent proof'</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>open - added 2026-09-06; upstream of the weak-field classical tests</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#143). ADDED BY REVIEW: the register had NO row for this at all, though foundations ledger #9 (2026-09-05) and gravity Staleness #69 both carry it. Reached independently by TWO OF THREE uncontaminated external runs from ED's axioms alone, before the corpus wrote it down; one proposed the fix a_C = (1/b_C)[-grad_adj Sigma_C], noting it 'directly contradicts P12 as literally stated - amending a primitive, not supplementing the axiom list'. The corpus's own check then WEAKENED it from contradiction to unproven on the measured inertia. Now also named in the report's walls section (14).</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
     <row r="438" ht="15.75" customHeight="1" s="39"/>
     <row r="439" ht="15.75" customHeight="1" s="39"/>
     <row r="440" ht="15.75" customHeight="1" s="39"/>
@@ -26181,7 +26227,7 @@
         </is>
       </c>
       <c r="E20" s="41" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="39"/>
@@ -27188,12 +27234,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B8"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="43.43" customWidth="1" style="39" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
@@ -27211,7 +27258,7 @@
         </is>
       </c>
       <c r="B3" s="33" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M437"/>
+  <dimension ref="A1:M440"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18.71" customWidth="1" style="39" min="1" max="1"/>
@@ -20685,55 +20685,193 @@
       </c>
     </row>
     <row r="437" ht="15.75" customHeight="1" s="39">
-      <c r="A437" t="inlineStr">
+      <c r="A437" s="0" t="inlineStr">
         <is>
           <t>Foundations</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B437" s="0" t="inlineStr">
         <is>
           <t>087</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C437" s="0" t="inlineStr">
         <is>
           <t>Universal free fall (equivalence-principle universality) under P12's literal a_C = -grad_adj Sigma_C</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
+      <c r="D437" s="0" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
+      <c r="F437" s="0" t="inlineStr">
         <is>
           <t>NOT established. P12 carries no inertial normalisation and the cross term scales as sqrt(b_K) in the chain's OWN bandwidth, so two chains of different bandwidth in one ambient field would accelerate differently</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr">
+      <c r="G437" s="0" t="inlineStr">
         <is>
           <t>OPEN. ED HAS an inertia mechanism and it is MEASURED - a bound composite under uniform force reaches v_x = 0.72 against an unbound cluster's 0.97 (Paper_MassWithoutMass_BindingInertia) - but that paper's preamble item 4 concedes the equivalence-principle reading is 'a consistent interpretation, not an independent proof'</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
+      <c r="H437" s="0" t="inlineStr">
         <is>
           <t>open - added 2026-09-06; upstream of the weak-field classical tests</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr">
+      <c r="K437" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#143). ADDED BY REVIEW: the register had NO row for this at all, though foundations ledger #9 (2026-09-05) and gravity Staleness #69 both carry it. Reached independently by TWO OF THREE uncontaminated external runs from ED's axioms alone, before the corpus wrote it down; one proposed the fix a_C = (1/b_C)[-grad_adj Sigma_C], noting it 'directly contradicts P12 as literally stated - amending a primitive, not supplementing the axiom list'. The corpus's own check then WEAKENED it from contradiction to unproven on the measured inertia. Now also named in the report's walls section (14).</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr">
+      <c r="M437" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
-    <row r="438" ht="15.75" customHeight="1" s="39"/>
-    <row r="439" ht="15.75" customHeight="1" s="39"/>
-    <row r="440" ht="15.75" customHeight="1" s="39"/>
+    <row r="438" ht="15.75" customHeight="1" s="39">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>019</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>YM-regime applicability: the Yang-Mills results hold in the SUB-PLANCKIAN KINEMATIC regime</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>A-&gt;regime (the qft arc ledger's own label)</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>a REGIME CONDITION, stated rather than derived; it scopes the continuum-YM results, it does not support them</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>current - scope condition on the Yang-Mills rows (019/021/022)</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#145). Found by C5a; read in its arc ledger before adding. ADDED because it is a SCOPE condition on results the register already carries (rows 80, 81, 82). Its absence meant a reader met the Yang-Mills results without the regime they hold in - the same linkage failure C4 found, one level up.</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="15.75" customHeight="1" s="39">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>QFT</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Osterwalder-Schrader composite verdict: 'structural-positive-conditional'</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Asserted</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>A-&gt;position (the qft arc ledger's own label)</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>a composite VERDICT over the OS reconstruction, not a separate derivation</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>current</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#145). Found by C5a; read in its arc ledger before adding. ADDED because the register carried the OS POSTULATE (row 263, P-OS-Reflection-Positivity, Postulated/live) but not the arc's VERDICT on what the reconstruction achieves. Postulate without standing is half the picture, and this is a Clay-adjacent claim where the standing is the point.</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="15.75" customHeight="1" s="39">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Soft-matter</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>086.5</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Photonic bandgap / negative index / cloaking reproduced from the two-scale expansion</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Inherited / Consilience</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>three D-via-I rows; the paper states NO D rows</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Bloch machinery, the two-scale expansion, effective-medium eps(w) and mu(w), and all designs are INHERITED</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>current - M2 (Intermediate Path C)</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-06 (#145). Found by C5a; read in its arc ledger before adding. ADDED at Inherited / Consilience, whose Tier Key definition is exactly this: 'Reproduces a known result/sequence framed THROUGH the substrate - supporting consilience, NOT a novel prediction.' Cross-domain reach is the corpus's central argument, so a reproduction with no D rows still belongs on the register - provided it is filed as consilience and not as a derivation, which is why the tier matters more than the row.</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
     <row r="441" ht="15.75" customHeight="1" s="39"/>
     <row r="442" ht="15.75" customHeight="1" s="39"/>
     <row r="443" ht="15.75" customHeight="1" s="39"/>
@@ -25951,7 +26089,7 @@
         </is>
       </c>
       <c r="E8" s="41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -26089,7 +26227,7 @@
         </is>
       </c>
       <c r="E14" s="41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -27308,7 +27446,7 @@
         </is>
       </c>
       <c r="B8" s="33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E2" s="40" t="inlineStr">
         <is>
-          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense) || DISCRIMINATOR (2026-08-02): a0=cH(z) [ED, RISES with z] vs a0=c2*sqrt(Lambda) [CONSTANT] coincide today but diverge with z; a0 following the sqrt(Lambda)-constant form rather than cH(z) refutes the ED relation. Recent high-z RAR literature (arXiv 2405.01841, 2504.20857) shows a MILD PREFERENCE for a0 rising with z -&gt; favors ED's cH(z) over the Lambda-tied form.</t>
+          <t>departs from cH(z)/2pi. Only 031 §8.8 is data-confronted: MUSE-DARK III (A&amp;A 2026) ~30sigma evolution, ~8% local, edge of H(z); alpha=1 the decisive open number. Do NOT over-bank (direction won, exact rate tense) || DISCRIMINATOR (2026-08-02): a0=cH(z) [ED, RISES with z] vs a0=c2*sqrt(Lambda) [CONSTANT] coincide today but diverge with z; a0 following the sqrt(Lambda)-constant form rather than cH(z) refutes the ED relation. Recent high-z RAR literature (arXiv 2405.01841, 2504.20857) shows a MILD PREFERENCE for a0 rising with z -&gt; favors ED's cH(z) over the Lambda-tied form. || 2026-09-07: exact rate COMPUTED at 2.3 sigma (alpha = 1.15 +/- 0.07); and the ~30sigma detection excludes constant-a0 MOND ONLY -- LCDM with baryons (Magneticum, MNRAS 10.1093/mnras/stac3017) also produces apparent a0 evolution, so evolution alone does not favour ED over LCDM.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="D46" s="41" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="E46" s="41" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="G46" s="41" t="inlineStr">
         <is>
-          <t>evolution CONFIRMED ~30sigma (MUSE-DARK III, A&amp;A 2026), excludes constant a0 / kills constant-scale MOND; EXACT rate ~H(z) in MILD TENSION (data run faster, ~1-few sigma, one survey)</t>
+          <t>evolution CONFIRMED ~30sigma (MUSE-DARK III, A&amp;A 2026), excludes constant a0 / kills constant-scale MOND. **2026-09-07: the ~30sigma does NOT separate ED from LCDM** -- Magneticum (MNRAS 10.1093/mnras/stac3017) shows plain LCDM WITH BARYONS produces an apparent rising a0 from galaxy assembly alone, no modified gravity. It excludes constant-a0 MOND and nothing else. EXACT rate: tension now COMPUTED, not estimated -- alpha = 1.15 +/- 0.07, alpha=1 at 2.3 sigma (event-density/theory/a0z_powerlaw_refit.py); the published +/-0.04 omits the intercept, cosmology and reduction choice = 73% of the variance. Survey systematics ON TOP and unquantified. NB their fit is LINEAR: alpha = 1.18 was always an ED-side recast, and their line has no constant exponent (local slope 1.78 -&gt; 0.90, crossing alpha=1 at z~1.1).</t>
         </is>
       </c>
       <c r="H46" s="41" t="inlineStr">
         <is>
-          <t>current — FLAGSHIP: direction won, exact rate under tension; do NOT over-bank (Rubin/Euclid decide)</t>
+          <t>current 2026-09-07 -- FLAGSHIP: evolution won, but it beats only constant-a0 MOND (not LCDM); exact rate 2.3 sigma against. Do NOT over-bank.</t>
         </is>
       </c>
       <c r="I46" s="41" t="inlineStr">
@@ -4047,7 +4047,11 @@
           <t>yes 2026-07-29</t>
         </is>
       </c>
-      <c r="J46" s="41" t="n"/>
+      <c r="J46" s="41" t="inlineStr">
+        <is>
+          <t>RE-TIERED Derived -&gt; Grounded 2026-09-07. Previously left at Derived on Paper_029 audit row 14 (evolution independent of the 2pi dispute), which is still true and is not the issue. The issue is a SECOND dependency named in Paper_a0z section 3.6 this session: the exponent also rests on the horizon being read LIVE rather than frozen, which that section calls 'the mechanism's core physical assertion, not a theorem' -- a frozen horizon gives alpha=0 and is indistinguishable from MOND. Workbook Derived requires NO paper-specific postulate; a live-horizon reading is one. Grounded is the correct tier: form-forced GIVEN that reading. The radial support is genuinely strong (R_H = c/H reached three independent ways, two of which never touch the dipole projection that failed to deliver the coefficient), which is why this is Grounded rather than Postulated.</t>
+        </is>
+      </c>
       <c r="K46" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#125). LEFT AT Derived DELIBERATELY. The formula embeds the disputed 1/(2pi), but Paper_029's audit row 14 states the EVOLUTION with exponent exactly 1 is D and independent of the coefficient dispute. The evolution is what this row claims. Flagged so the 2pi inside the formula is not read as settled.</t>
@@ -4055,7 +4059,7 @@
       </c>
       <c r="M46" s="0" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -14502,12 +14506,12 @@
       <c r="F288" s="41" t="n"/>
       <c r="G288" s="41" t="inlineStr">
         <is>
-          <t>(see Falsifier); ONLY 031 §8.8 reflects the 2026 data</t>
+          <t>(see Falsifier); ONLY 031 §8.8 reflects the 2026 data || 2026-09-07: exact rate now COMPUTED at 2.3 sigma (alpha = 1.15 +/- 0.07), and the ~30sigma excludes constant-a0 MOND only -- LCDM with baryons (Magneticum) also gives apparent evolution.</t>
         </is>
       </c>
       <c r="H288" s="41" t="inlineStr">
         <is>
-          <t>current — flagship; ~30sigma evolution confirmed, exact rate alpha=1 the open number (Staleness #1)</t>
+          <t>current 2026-09-07 -- flagship; ~30sigma evolution confirmed but does not beat LCDM; exact rate 2.3 sigma against (computed, not estimated)</t>
         </is>
       </c>
       <c r="I288" s="41" t="inlineStr">
@@ -14518,7 +14522,7 @@
       <c r="J288" s="41" t="n"/>
       <c r="M288" s="0" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -20732,141 +20736,141 @@
       </c>
     </row>
     <row r="438" ht="15.75" customHeight="1" s="39">
-      <c r="A438" t="inlineStr">
+      <c r="A438" s="0" t="inlineStr">
         <is>
           <t>QFT</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
+      <c r="B438" s="0" t="inlineStr">
         <is>
           <t>019</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr">
+      <c r="C438" s="0" t="inlineStr">
         <is>
           <t>YM-regime applicability: the Yang-Mills results hold in the SUB-PLANCKIAN KINEMATIC regime</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr">
+      <c r="D438" s="0" t="inlineStr">
         <is>
           <t>Asserted</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr">
+      <c r="F438" s="0" t="inlineStr">
         <is>
           <t>A-&gt;regime (the qft arc ledger's own label)</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr">
+      <c r="G438" s="0" t="inlineStr">
         <is>
           <t>a REGIME CONDITION, stated rather than derived; it scopes the continuum-YM results, it does not support them</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
+      <c r="H438" s="0" t="inlineStr">
         <is>
           <t>current - scope condition on the Yang-Mills rows (019/021/022)</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr">
+      <c r="K438" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#145). Found by C5a; read in its arc ledger before adding. ADDED because it is a SCOPE condition on results the register already carries (rows 80, 81, 82). Its absence meant a reader met the Yang-Mills results without the regime they hold in - the same linkage failure C4 found, one level up.</t>
         </is>
       </c>
-      <c r="M438" t="inlineStr">
+      <c r="M438" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="439" ht="15.75" customHeight="1" s="39">
-      <c r="A439" t="inlineStr">
+      <c r="A439" s="0" t="inlineStr">
         <is>
           <t>QFT</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
+      <c r="B439" s="0" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
+      <c r="C439" s="0" t="inlineStr">
         <is>
           <t>Osterwalder-Schrader composite verdict: 'structural-positive-conditional'</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr">
+      <c r="D439" s="0" t="inlineStr">
         <is>
           <t>Asserted</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr">
+      <c r="F439" s="0" t="inlineStr">
         <is>
           <t>A-&gt;position (the qft arc ledger's own label)</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr">
+      <c r="G439" s="0" t="inlineStr">
         <is>
           <t>a composite VERDICT over the OS reconstruction, not a separate derivation</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
+      <c r="H439" s="0" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr">
+      <c r="K439" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#145). Found by C5a; read in its arc ledger before adding. ADDED because the register carried the OS POSTULATE (row 263, P-OS-Reflection-Positivity, Postulated/live) but not the arc's VERDICT on what the reconstruction achieves. Postulate without standing is half the picture, and this is a Clay-adjacent claim where the standing is the point.</t>
         </is>
       </c>
-      <c r="M439" t="inlineStr">
+      <c r="M439" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="440" ht="15.75" customHeight="1" s="39">
-      <c r="A440" t="inlineStr">
+      <c r="A440" s="0" t="inlineStr">
         <is>
           <t>Soft-matter</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B440" s="0" t="inlineStr">
         <is>
           <t>086.5</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C440" s="0" t="inlineStr">
         <is>
           <t>Photonic bandgap / negative index / cloaking reproduced from the two-scale expansion</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
+      <c r="D440" s="0" t="inlineStr">
         <is>
           <t>Inherited / Consilience</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
+      <c r="F440" s="0" t="inlineStr">
         <is>
           <t>three D-via-I rows; the paper states NO D rows</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
+      <c r="G440" s="0" t="inlineStr">
         <is>
           <t>Bloch machinery, the two-scale expansion, effective-medium eps(w) and mu(w), and all designs are INHERITED</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
+      <c r="H440" s="0" t="inlineStr">
         <is>
           <t>current - M2 (Intermediate Path C)</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr">
+      <c r="K440" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-06 (#145). Found by C5a; read in its arc ledger before adding. ADDED at Inherited / Consilience, whose Tier Key definition is exactly this: 'Reproduces a known result/sequence framed THROUGH the substrate - supporting consilience, NOT a novel prediction.' Cross-domain reach is the corpus's central argument, so a reproduction with no D rows still belongs on the register - provided it is filed as consilience and not as a derivation, which is why the tier matters more than the row.</t>
         </is>
       </c>
-      <c r="M440" t="inlineStr">
+      <c r="M440" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
@@ -27386,7 +27390,7 @@
         </is>
       </c>
       <c r="B2" s="34" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -27416,7 +27420,7 @@
         </is>
       </c>
       <c r="B5" s="34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -10053,7 +10053,7 @@
       </c>
       <c r="H179" s="41" t="inlineStr">
         <is>
-          <t>current — Grounded (gauge-law-forced); sign supplied at Measured tier</t>
+          <t>current - Grounded (gauge-law-forced); sign STRUCTURALLY SETTLED 2026-09-07, not awaiting a measurement</t>
         </is>
       </c>
       <c r="I179" s="41" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="L179" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
+          <t>STRUCTURALLY SETTLED 2026-09-05 (foundations #10, internal notes/_check_sigma_sign.py); sign invariant RECORDED: P12 gives a_C = -grad_adj Sigma_C, so radially a_r = -d(Sigma_C)/dR. Newton ~ 1/R and MOND ~ ln R have opposite radial derivatives, so both being attractive forces the two pieces into Sigma_C with OPPOSITE signs -- Str the diagonal, Coh the off-diagonal. Coh then enters with a plus, so cos Theta_LH &gt; 0 follows from the assignment. This row is the ANALYTIC claim, so it is settled outright: no measurement is owed by it. Its old Status line 'sign supplied at Measured tier' is superseded -- the sign is supplied structurally.</t>
         </is>
       </c>
       <c r="M179" s="0" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H191" s="41" t="inlineStr">
         <is>
-          <t>CORRECTED 2026-09-06 - claim read '(P12-Coh rewards alignment)' and 'conditional on P12-Coh operationalization'</t>
+          <t>CORRECTED 2026-09-06 - claim read '(P12-Coh rewards alignment)' and 'conditional on P12-Coh operationalization' || 2026-09-07: sign STRUCTURALLY SETTLED; MEASURED CORROBORATION CANDIDATE (same vocabulary as the Report's MOND section).</t>
         </is>
       </c>
       <c r="I191" s="41" t="n"/>
@@ -10565,7 +10565,12 @@
       </c>
       <c r="L191" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
+          <t>STRUCTURALLY SETTLED 2026-09-05 (foundations #10, internal notes/_check_sigma_sign.py); measured corroboration CANDIDATE. sign invariant RECORDED: P12 gives a_C = -grad_adj Sigma_C, so radially a_r = -d(Sigma_C)/dR. Newton ~ 1/R and MOND ~ ln R have opposite radial derivatives, so both being attractive forces the two pieces into Sigma_C with OPPOSITE signs -- Str the diagonal, Coh the off-diagonal. Coh then enters with a plus, so cos Theta_LH &gt; 0 follows from the assignment. The structural route is independent of the build, which matters here because gravity ledger #112 found the build measured Grad, not canonical Coh. The sign transfers anyway (+Coh and -Grad both reward alignment); what does NOT transfer is measured confirmation of canonical Coh.</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10893,7 @@
       </c>
       <c r="H199" s="41" t="inlineStr">
         <is>
-          <t>CORRECTED 2026-09-06 - read 'P12 coherence rewards alignment but stays FINITE-REACH'; the measured object is Grad</t>
+          <t>CORRECTED 2026-09-06 - read 'P12 coherence rewards alignment but stays FINITE-REACH'; the measured object is Grad || 2026-09-07: sign STRUCTURALLY SETTLED; MEASURED CORROBORATION CANDIDATE (same vocabulary as the Report's MOND section).</t>
         </is>
       </c>
       <c r="I199" s="41" t="n"/>
@@ -10900,7 +10905,12 @@
       </c>
       <c r="L199" s="0" t="inlineStr">
         <is>
-          <t>CANDIDATE - confirm, and record the invariant that fixes the sign</t>
+          <t>STRUCTURALLY SETTLED 2026-09-05 (foundations #10, internal notes/_check_sigma_sign.py); measured corroboration CANDIDATE, and this is the row where that distinction bites. sign invariant RECORDED: P12 gives a_C = -grad_adj Sigma_C, so radially a_r = -d(Sigma_C)/dR. Newton ~ 1/R and MOND ~ ln R have opposite radial derivatives, so both being attractive forces the two pieces into Sigma_C with OPPOSITE signs -- Str the diagonal, Coh the off-diagonal. Coh then enters with a plus, so cos Theta_LH &gt; 0 follows from the assignment. Per #111, canonical Coh shows NO alignment gain under any normalisation tried, so the measured finite-reach result is a property of Grad intensively scored and does not transfer. The SIGN is unaffected: it never depended on this run.</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -27376,13 +27386,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A2:B8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="43.43" customWidth="1" style="39" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -4034,12 +4034,12 @@
       </c>
       <c r="G46" s="41" t="inlineStr">
         <is>
-          <t>evolution CONFIRMED ~30sigma (MUSE-DARK III, A&amp;A 2026), excludes constant a0 / kills constant-scale MOND. **2026-09-07: the ~30sigma does NOT separate ED from LCDM** -- Magneticum (MNRAS 10.1093/mnras/stac3017) shows plain LCDM WITH BARYONS produces an apparent rising a0 from galaxy assembly alone, no modified gravity. It excludes constant-a0 MOND and nothing else. EXACT rate: tension now COMPUTED, not estimated -- alpha = 1.15 +/- 0.07, alpha=1 at 2.3 sigma (event-density/theory/a0z_powerlaw_refit.py); the published +/-0.04 omits the intercept, cosmology and reduction choice = 73% of the variance. Survey systematics ON TOP and unquantified. NB their fit is LINEAR: alpha = 1.18 was always an ED-side recast, and their line has no constant exponent (local slope 1.78 -&gt; 0.90, crossing alpha=1 at z~1.1).</t>
+          <t>evolution CONFIRMED ~30sigma (MUSE-DARK III, A&amp;A 2026), excludes constant a0 / kills constant-scale MOND. **2026-09-07: the ~30sigma does NOT separate ED from LCDM** -- Magneticum (MNRAS 10.1093/mnras/stac3017) shows plain LCDM WITH BARYONS produces an apparent rising a0 from galaxy assembly alone, no modified gravity. It excludes constant-a0 MOND and nothing else. EXACT rate: tension now COMPUTED, not estimated -- alpha = 1.15 +/- 0.07, alpha=1 at 2.3 sigma (event-density/theory/a0z_powerlaw_refit.py); the published +/-0.04 omits the intercept, cosmology and reduction choice = 73% of the variance. Survey systematics ON TOP and unquantified. NB their fit is LINEAR: alpha = 1.18 was always an ED-side recast, and their line has no constant exponent (local slope 1.78 -&gt; 0.90, crossing alpha=1 at z~1.1). || 2026-09-07 ROUND 3: the systematics challenge is REAL and located - Rusishvili 2026 (academia.edu/170831186, self-posted, NOT peer-reviewed) re-analyses Ciocan's own public catalogue and reports three baryonic systematics, each claimed sufficient. Effect sizes are QUANTITATIVELY COHERENT (checked: theory/a0z_baryonic_systematics_check.py - the claimed 82%% from molecular gas falls out at M_HI/M* ~ 0.1, the expected regime, with no free parameter). It attacks the ~30sigma DETECTION, not just the rate. If it holds, the qualitative win AND the 2.3sigma tension go together and the honest status is UNTESTED. DO NOT BANK EITHER.</t>
         </is>
       </c>
       <c r="H46" s="41" t="inlineStr">
         <is>
-          <t>current 2026-09-07 -- FLAGSHIP: evolution won, but it beats only constant-a0 MOND (not LCDM); exact rate 2.3 sigma against. Do NOT over-bank.</t>
+          <t>OPEN 2026-09-07 - flagship, but the one survey testing it is itself under a coherent systematics challenge; status UNTESTED rather than confirmed-or-refuted. Do NOT over-bank in either direction.</t>
         </is>
       </c>
       <c r="I46" s="41" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H120" s="41" t="inlineStr">
         <is>
-          <t>current — THE STANDING MOND RESULT; do not reinvent</t>
+          <t>CURRENT - standing relativistic MOND embedding; do not reinvent. BUT the high-acceleration canonicalization remains OPEN (2026-09-07): KM-I uses a smooth Cassini-constrained family, Paper_030 a high-acceleration switch; neither is falsified and the canonical choice is unresolved. 'Standing' is the result, not the implementation.</t>
         </is>
       </c>
       <c r="I120" s="41" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="M120" s="0" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
           <t>STRUCTURALLY SETTLED 2026-09-05 (foundations #10, internal notes/_check_sigma_sign.py); measured corroboration CANDIDATE. sign invariant RECORDED: P12 gives a_C = -grad_adj Sigma_C, so radially a_r = -d(Sigma_C)/dR. Newton ~ 1/R and MOND ~ ln R have opposite radial derivatives, so both being attractive forces the two pieces into Sigma_C with OPPOSITE signs -- Str the diagonal, Coh the off-diagonal. Coh then enters with a plus, so cos Theta_LH &gt; 0 follows from the assignment. The structural route is independent of the build, which matters here because gravity ledger #112 found the build measured Grad, not canonical Coh. The sign transfers anyway (+Coh and -Grad both reward alignment); what does NOT transfer is measured confirmation of canonical Coh.</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr">
+      <c r="M191" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -10908,7 +10908,7 @@
           <t>STRUCTURALLY SETTLED 2026-09-05 (foundations #10, internal notes/_check_sigma_sign.py); measured corroboration CANDIDATE, and this is the row where that distinction bites. sign invariant RECORDED: P12 gives a_C = -grad_adj Sigma_C, so radially a_r = -d(Sigma_C)/dR. Newton ~ 1/R and MOND ~ ln R have opposite radial derivatives, so both being attractive forces the two pieces into Sigma_C with OPPOSITE signs -- Str the diagonal, Coh the off-diagonal. Coh then enters with a plus, so cos Theta_LH &gt; 0 follows from the assignment. Per #111, canonical Coh shows NO alignment gain under any normalisation tried, so the measured finite-reach result is a property of Grad intensively scored and does not transfer. The SIGN is unaffected: it never depended on this run.</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
+      <c r="M199" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -14516,12 +14516,12 @@
       <c r="F288" s="41" t="n"/>
       <c r="G288" s="41" t="inlineStr">
         <is>
-          <t>(see Falsifier); ONLY 031 §8.8 reflects the 2026 data || 2026-09-07: exact rate now COMPUTED at 2.3 sigma (alpha = 1.15 +/- 0.07), and the ~30sigma excludes constant-a0 MOND only -- LCDM with baryons (Magneticum) also gives apparent evolution.</t>
+          <t>(see Falsifier); ONLY 031 §8.8 reflects the 2026 data || 2026-09-07: exact rate now COMPUTED at 2.3 sigma (alpha = 1.15 +/- 0.07), and the ~30sigma excludes constant-a0 MOND only -- LCDM with baryons (Magneticum) also gives apparent evolution. || 2026-09-07 ROUND 3: the systematics challenge is REAL and located - Rusishvili 2026 (academia.edu/170831186, self-posted, NOT peer-reviewed) re-analyses Ciocan's own public catalogue and reports three baryonic systematics, each claimed sufficient. Effect sizes are QUANTITATIVELY COHERENT (checked: theory/a0z_baryonic_systematics_check.py - the claimed 82%% from molecular gas falls out at M_HI/M* ~ 0.1, the expected regime, with no free parameter). It attacks the ~30sigma DETECTION, not just the rate. If it holds, the qualitative win AND the 2.3sigma tension go together and the honest status is UNTESTED. DO NOT BANK EITHER.</t>
         </is>
       </c>
       <c r="H288" s="41" t="inlineStr">
         <is>
-          <t>current 2026-09-07 -- flagship; ~30sigma evolution confirmed but does not beat LCDM; exact rate 2.3 sigma against (computed, not estimated)</t>
+          <t>OPEN 2026-09-07 - flagship, but the one survey testing it is itself under a coherent systematics challenge; status UNTESTED rather than confirmed-or-refuted. Do NOT over-bank in either direction.</t>
         </is>
       </c>
       <c r="I288" s="41" t="inlineStr">
@@ -17489,7 +17489,7 @@
       </c>
       <c r="C362" s="41" t="inlineStr">
         <is>
-          <t>MOND = the off-diagonal HORIZON-INTERFERENCE cross-term; sqrt(a_N a0) forced GIVEN P14 + the bilocal-channel construction (scoped 2026-09-04)</t>
+          <t>MOND = the off-diagonal HORIZON-INTERFERENCE cross-term; sqrt(a_N a0) forced GIVEN P-Quadratic-Strain + the bilocal-channel construction (re-scoped 2026-09-07: was 'GIVEN P14', but P14 is the postulate the quadratic-strain construction DISCHARGES, so citing it as the dependency inverted the relation). Paper_030 §5.3's regime assumption is RESTORED and is a separate, live dependency.</t>
         </is>
       </c>
       <c r="D362" s="41" t="inlineStr">
@@ -17521,7 +17521,7 @@
       <c r="J362" s="41" t="n"/>
       <c r="M362" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -18235,12 +18235,12 @@
       <c r="F380" s="41" t="n"/>
       <c r="G380" s="41" t="inlineStr">
         <is>
-          <t>discharges P14 (geometric mean = forced interference modulus) + 030's regime assumption (horizon is a dipole not a monopole); STRUCTURAL, conditional on P-Quadratic-Strain; residual = constructive sign (measured tier)</t>
+          <t>REWRITTEN 2026-09-07; all three clauses were stale. (1) The P14 discharge stands and is the STRONG half, but the row's dependency is now P-Quadratic-Strain, not P14. (2) Paper_030's regime assumption was NOT discharged - it was RESTORED, so 'two postulates to one' reads ONE AND A HALF. (3) The residual is NOT 'constructive sign': that is STRUCTURALLY SETTLED (foundations #10 - a_r = -dSigma/dR, Newton ~1/R and MOND ~ln R have opposite radial derivatives, so Coh enters with a plus and cos Theta_LH &gt; 0 follows). What remains is MEASURED CORROBORATION of canonical Coh, which is candidate because the build measured Grad (#112). Live residuals: threshold generation from a linear horizon response, high-acceleration canonicalization, UFF normalization.</t>
         </is>
       </c>
       <c r="H380" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current 2026-09-07 - STRUCTURAL, conditional on P-Quadratic-Strain; regime assumption restored; sign structurally settled, measured corroboration candidate</t>
         </is>
       </c>
       <c r="I380" s="41" t="inlineStr">
@@ -18251,7 +18251,7 @@
       <c r="J380" s="41" t="n"/>
       <c r="M380" s="0" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -3294,6 +3294,16 @@
       </c>
       <c r="I29" s="41" t="n"/>
       <c r="J29" s="41" t="n"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper's own audit row reads 'D-via-I | Composition of P-V5-UV-Cutoff + P-Cutoff-Saturation'. CONFIRMED verbatim.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="39">
       <c r="A30" s="41" t="inlineStr">
@@ -3334,6 +3344,16 @@
       </c>
       <c r="I30" s="41" t="n"/>
       <c r="J30" s="41" t="n"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. conditional structural derivation; value INHERITED via matching to Paper_048's higher-order resummation. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="39">
       <c r="A31" s="41" t="inlineStr">
@@ -3623,6 +3643,16 @@
       </c>
       <c r="I37" s="41" t="n"/>
       <c r="J37" s="41" t="n"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper is a 'conditional structural derivation given the 13 ED primitives + declared paper-specific postulates', with the thermal content INHERITED from semi-classical GR. Form derived, values inherited = D-via-I. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="39">
       <c r="A38" s="41" t="inlineStr">
@@ -4410,7 +4440,12 @@
       <c r="J53" s="41" t="n"/>
       <c r="K53" s="0" t="inlineStr">
         <is>
-          <t>P-Continuity, P-Additivity, P-Maximality (audit rows 3-5, all P); normalization inherited. VERIFIED 2026-09-06 (#124), read against the paper's own audit table. The sheet's own Derived column already read 'D-via-I', contradicting the Derived tier. P-Maximality's derivation (O-vN-2) is not merely open but STRUCTURALLY BLOCKED - ED has no substrate-level temperature. [re-tiered Derived -&gt; Grounded]</t>
+          <t>P-Continuity, P-Additivity, P-Maximality (audit rows 3-5, all P); normalization inherited. VERIFIED 2026-09-06 (#124), read against the paper's own audit table. The sheet's own Derived column already read 'D-via-I', contradicting the Derived tier. P-Maximality's derivation (O-vN-2) is not merely open but STRUCTURALLY BLOCKED - ED has no substrate-level temperature. [re-tiered Derived -&gt; Grounded] || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. conditional structural derivation; normalisation INHERITED via standard-QM matching; two substrate-derivations remain open and are separately rowed. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4490,12 @@
       <c r="J54" s="41" t="n"/>
       <c r="K54" s="0" t="inlineStr">
         <is>
-          <t>P-SubstrateLocality. VERIFIED 2026-09-06 (#125). The row's own cell already read: leans on an explicit P-SubstrateLocality postulate.</t>
+          <t>P-SubstrateLocality. VERIFIED 2026-09-06 (#125). The row's own cell already read: leans on an explicit P-SubstrateLocality postulate. || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper states 'conditional: given the 13 primitives + substrate-operational compositional closure, V1 has finite-width retarded form'. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4684,12 @@
       <c r="J58" s="41" t="n"/>
       <c r="K58" s="0" t="inlineStr">
         <is>
-          <t>P-Codim-1, P-Sat; l_ED value inherited. VERIFIED 2026-09-06 (#125).</t>
+          <t>P-Codim-1, P-Sat; l_ED value inherited. VERIFIED 2026-09-06 (#125). || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper states 'conditional on the substrate ontology'. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4734,12 @@
       <c r="J59" s="41" t="n"/>
       <c r="K59" s="0" t="inlineStr">
         <is>
-          <t>P-Potential-Reading (Model A); V1 1/R envelope inherited via DCGT. VERIFIED 2026-09-06 (#125).</t>
+          <t>P-Potential-Reading (Model A); V1 1/R envelope inherited via DCGT. VERIFIED 2026-09-06 (#125). || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. audit 2.5: rests on P-Potential-Reading (P) + P-Codim-1 (P, inherited from 025) + the V1 1/R envelope (I, from 073 DCGT, explicitly 'not derived in this paper'); all remaining steps D. Postulate-conditional = Grounded. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4879,12 @@
       <c r="J62" s="41" t="n"/>
       <c r="K62" s="0" t="inlineStr">
         <is>
-          <t>P-H0-Cosmological-Invariant. VERIFIED 2026-09-06 (#125).</t>
+          <t>P-H0-Cosmological-Invariant. VERIFIED 2026-09-06 (#125). || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper states 'conditional structural derivation given the 13 ED primitives + paper-specific postulates'; H0 INHERITED as the cosmological-rate parameter. CONFIRMED.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/ED_ItemizedTheory_TieredClaims_v2.xlsx
+++ b/ED_ItemizedTheory_TieredClaims_v2.xlsx
@@ -2925,7 +2925,7 @@
       </c>
       <c r="H20" s="41" t="inlineStr">
         <is>
-          <t>STALE AS OF 2026-09-04 — was 'current'. The 1/(2pi) is re-tiered **Postulated/disputed** (gravity Staleness #10): it cancels in Paper_028 §6.3 / Paper_029 §5.1's own displayed algebra. The SCALE a0 ~ cH0 stands and is now reached FOUR independent ways (dipole projection; Rindler/de Sitter smoothness; horizon-competition threshold #34; content-depth #38) — none reaches the coefficient. Empirical standing tightened 2026-09-04: Desmond 2023 (a0 = 1.19 ± 0.04 ± 0.09) puts the 2pi at 1.09 sigma (was 0.49 sigma vs the 2016 systematic), and it PREFERS A HIGH H0 — 1.50 sigma vs Planck, 0.62 sigma vs SH0ES. See Paper_029 §5.5, Staleness #39</t>
+          <t>Current status: superseded — see the correction that follows. || Historical correction: STALE AS OF 2026-09-04 — was 'current'. The 1/(2pi) is re-tiered **Postulated/disputed** (gravity Staleness #10): it cancels in Paper_028 §6.3 / Paper_029 §5.1's own displayed algebra. The SCALE a0 ~ cH0 stands and is now reached FOUR independent ways (dipole projection; Rindler/de Sitter smoothness; horizon-competition threshold #34; content-depth #38) — none reaches the coefficient. Empirical standing tightened 2026-09-04: Desmond 2023 (a0 = 1.19 ± 0.04 ± 0.09) puts the 2pi at 1.09 sigma (was 0.49 sigma vs the 2016 systematic), and it PREFERS A HIGH H0 — 1.50 sigma vs Planck, 0.62 sigma vs SH0ES. See Paper_029 §5.5, Staleness #39</t>
         </is>
       </c>
       <c r="I20" s="41" t="n"/>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="I29" s="41" t="n"/>
       <c r="J29" s="41" t="n"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper's own audit row reads 'D-via-I | Composition of P-V5-UV-Cutoff + P-Cutoff-Saturation'. CONFIRMED verbatim.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="I30" s="41" t="n"/>
       <c r="J30" s="41" t="n"/>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. conditional structural derivation; value INHERITED via matching to Paper_048's higher-order resummation. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="I37" s="41" t="n"/>
       <c r="J37" s="41" t="n"/>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t>VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper is a 'conditional structural derivation given the 13 ED primitives + declared paper-specific postulates', with the thermal content INHERITED from semi-classical GR. Form derived, values inherited = D-via-I. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -4443,7 +4443,7 @@
           <t>P-Continuity, P-Additivity, P-Maximality (audit rows 3-5, all P); normalization inherited. VERIFIED 2026-09-06 (#124), read against the paper's own audit table. The sheet's own Derived column already read 'D-via-I', contradicting the Derived tier. P-Maximality's derivation (O-vN-2) is not merely open but STRUCTURALLY BLOCKED - ED has no substrate-level temperature. [re-tiered Derived -&gt; Grounded] || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. conditional structural derivation; normalisation INHERITED via standard-QM matching; two substrate-derivations remain open and are separately rowed. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -4493,7 +4493,7 @@
           <t>P-SubstrateLocality. VERIFIED 2026-09-06 (#125). The row's own cell already read: leans on an explicit P-SubstrateLocality postulate. || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper states 'conditional: given the 13 primitives + substrate-operational compositional closure, V1 has finite-width retarded form'. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M54" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -4687,7 +4687,7 @@
           <t>P-Codim-1, P-Sat; l_ED value inherited. VERIFIED 2026-09-06 (#125). || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper states 'conditional on the substrate ontology'. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -4737,7 +4737,7 @@
           <t>P-Potential-Reading (Model A); V1 1/R envelope inherited via DCGT. VERIFIED 2026-09-06 (#125). || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. audit 2.5: rests on P-Potential-Reading (P) + P-Codim-1 (P, inherited from 025) + the V1 1/R envelope (I, from 073 DCGT, explicitly 'not derived in this paper'); all remaining steps D. Postulate-conditional = Grounded. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -4882,7 +4882,7 @@
           <t>P-H0-Cosmological-Invariant. VERIFIED 2026-09-06 (#125). || VERIFIED 2026-09-07 (highest-reach undated sweep): read the paper's own audit and confirmed the tier against it. paper states 'conditional structural derivation given the 13 ED primitives + paper-specific postulates'; H0 INHERITED as the cosmological-rate parameter. CONFIRMED.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M62" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
